--- a/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
+++ b/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
@@ -28299,11 +28299,15 @@
       <c r="H6" s="14" t="n"/>
       <c r="I6" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="J6" s="16" t="n"/>
-      <c r="K6" s="14" t="n"/>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>Cannot verify remotely - needs direct server/file/hosting access this agent doesn't have (CLAUDE.md bucket 4). Still 'Not Started' as of 2026-10-01, three weeks after the audit - this is the single highest-urgency open item in the whole tracker. Step-by-step checklist in docs/seo/technical/TECH-runbook.md Phase 1.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="23.25" customHeight="1" s="23">
       <c r="A7" s="17" t="inlineStr">
@@ -28344,11 +28348,15 @@
       <c r="H7" s="14" t="n"/>
       <c r="I7" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="J7" s="16" t="n"/>
-      <c r="K7" s="14" t="n"/>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>Needs WordPress admin/hosting/FTP/database access this agent doesn't have. Checklist in docs/seo/technical/TECH-runbook.md Phase 1 - do regardless of what TECH-01 finds.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="34.5" customHeight="1" s="23">
       <c r="A8" s="11" t="inlineStr">
@@ -28389,11 +28397,15 @@
       <c r="H8" s="14" t="n"/>
       <c r="I8" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J8" s="16" t="n"/>
-      <c r="K8" s="14" t="n"/>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>Confirmed via public site: search (2026-10-01): the specific spam-era URLs (/tag/smoking/, /tag/gene-therapy/) no longer appear in Google's index for this domain - consistent with the tracker's note that spam dropped out naturally. But tag archives in general are still indexed (legitimate ones like /tag/gluten/, /tag/alcohol/, /tag/abhrs/ are live right now), so the underlying surface is still open. The noindex fix itself needs Rank Math/WP admin access this agent doesn't have. See docs/seo/technical/TECH-runbook.md Phase 2.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="34.5" customHeight="1" s="23">
       <c r="A9" s="17" t="inlineStr">
@@ -28434,11 +28446,15 @@
       <c r="H9" s="14" t="n"/>
       <c r="I9" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J9" s="16" t="n"/>
-      <c r="K9" s="14" t="n"/>
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>Checked whether this is possible via the Search Console API this agent has - it is not. Manual actions/Security issues are only exposed through the Search Console web UI, not the API surface available here. Needs someone to log into search.google.com/search-console directly. See docs/seo/technical/TECH-runbook.md Phase 1.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="23.25" customHeight="1" s="23">
       <c r="A10" s="11" t="inlineStr">
@@ -28479,11 +28495,15 @@
       <c r="H10" s="14" t="n"/>
       <c r="I10" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J10" s="16" t="n"/>
-      <c r="K10" s="14" t="n"/>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>Covered by the TECH-03 fix once applied. Confirming paginated variants specifically needs the Search Console Pages report (UI only). See docs/seo/technical/TECH-runbook.md Phase 2.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="45.75" customHeight="1" s="23">
       <c r="A11" s="17" t="inlineStr">
@@ -28524,11 +28544,15 @@
       <c r="H11" s="14" t="n"/>
       <c r="I11" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="J11" s="16" t="n"/>
-      <c r="K11" s="14" t="n"/>
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>Needs WordPress/Elementor admin access this agent doesn't have.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="34.5" customHeight="1" s="23">
       <c r="A12" s="11" t="inlineStr">
@@ -28569,11 +28593,15 @@
       <c r="H12" s="14" t="n"/>
       <c r="I12" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="J12" s="16" t="n"/>
-      <c r="K12" s="14" t="n"/>
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>Still blocked as of 2026-10-01: the DataForSEO Lighthouse action errored on this domain earlier in the engagement (ERRORED_DOCUMENT_REQUEST, likely the host's bot protection), and the workspace's DataForSEO credits were at zero on last check. Manual PageSpeed Insights checklist in docs/seo/technical/TECH-runbook.md Phase 4.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="45.75" customHeight="1" s="23">
       <c r="A13" s="17" t="inlineStr">
@@ -28614,11 +28642,15 @@
       <c r="H13" s="14" t="n"/>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J13" s="16" t="n"/>
-      <c r="K13" s="14" t="n"/>
+      <c r="K13" s="14" t="inlineStr">
+        <is>
+          <t>Diagnosed precisely (2026-09-11, reconfirmed 2026-10-01): the account has siteOwner permission on the URL-prefix property (https://drranairfan.com/) but only siteUnverifiedUser on the domain property (sc-domain:drranairfan.com) - confirmed via google_search_console.site_list. That's exactly why queries against the domain property were failing (HTTP 403) while the URL-prefix property works. Actually fixing this needs someone to complete Google's domain verification (DNS TXT record) in Search Console directly - outside what an API call can do. See docs/seo/technical/TECH-runbook.md Phase 4.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="23.25" customHeight="1" s="23">
       <c r="A14" s="11" t="inlineStr">
@@ -28659,11 +28691,15 @@
       <c r="H14" s="14" t="n"/>
       <c r="I14" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="J14" s="16" t="n"/>
-      <c r="K14" s="14" t="n"/>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>Needs wp-config.php/hosting file access this agent doesn't have.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="34.5" customHeight="1" s="23">
       <c r="A15" s="17" t="inlineStr">
@@ -28704,11 +28740,15 @@
       <c r="H15" s="14" t="n"/>
       <c r="I15" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="J15" s="16" t="n"/>
-      <c r="K15" s="14" t="n"/>
+      <c r="K15" s="14" t="inlineStr">
+        <is>
+          <t>Needs WordPress admin access this agent doesn't have.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="34.5" customHeight="1" s="23">
       <c r="A16" s="11" t="inlineStr">
@@ -28749,11 +28789,15 @@
       <c r="H16" s="14" t="n"/>
       <c r="I16" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="J16" s="16" t="n"/>
-      <c r="K16" s="14" t="n"/>
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>Attempted to fetch https://drranairfan.com/robots.txt directly (2026-10-01) - this environment's network policy blocks fetching the domain itself (EGRESS_BLOCKED), not just third-party sites. Zero information obtained; needs someone with normal browser/terminal access to check.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="34.5" customHeight="1" s="23">
       <c r="A17" s="17" t="inlineStr">
@@ -28794,11 +28838,15 @@
       <c r="H17" s="14" t="n"/>
       <c r="I17" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="J17" s="16" t="n"/>
-      <c r="K17" s="14" t="n"/>
+      <c r="K17" s="14" t="inlineStr">
+        <is>
+          <t>Same EGRESS_BLOCKED issue as TECH-11 - could not fetch the sitemap to review its contents. Once reviewed and confirmed clean, resubmitting via Search Console is something this agent can do on request (google_search_console.sitemap_submit) but is a live external action needing explicit go-ahead per CLAUDE.md bucket 2, not something to do unprompted.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="23.25" customHeight="1" s="23">
       <c r="A18" s="11" t="inlineStr">
@@ -28839,11 +28887,15 @@
       <c r="H18" s="14" t="n"/>
       <c r="I18" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J18" s="16" t="n"/>
-      <c r="K18" s="14" t="n"/>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>Partially checked via site:drranairfan.com search rather than the Search Console Pages report (UI only) - tag and category archives confirmed still in the index alongside genuine content. Full indexed-vs-intended comparison still needs the Pages report directly.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="23.25" customHeight="1" s="23">
       <c r="A19" s="17" t="inlineStr">
@@ -28884,11 +28936,15 @@
       <c r="H19" s="14" t="n"/>
       <c r="I19" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J19" s="16" t="n"/>
-      <c r="K19" s="14" t="n"/>
+      <c r="K19" s="14" t="inlineStr">
+        <is>
+          <t>Confirmed via site: search (2026-10-01): /category/facial/ is still indexed, currently showing legitimate content (Hydrafacial/beard transplant articles, not spam) rather than what it carried during the compromise - but it's still exactly the kind of thin auto-generated archive the tracker flags. The fix (noindex or curate into real hub pages) needs WP admin access.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="34.5" customHeight="1" s="23">
       <c r="A20" s="11" t="inlineStr">
@@ -28929,11 +28985,15 @@
       <c r="H20" s="14" t="n"/>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="J20" s="16" t="n"/>
-      <c r="K20" s="14" t="n"/>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>Needs WordPress admin access this agent doesn't have.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="34.5" customHeight="1" s="23">
       <c r="A21" s="17" t="inlineStr">
@@ -28974,11 +29034,15 @@
       <c r="H21" s="14" t="n"/>
       <c r="I21" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="J21" s="16" t="n"/>
-      <c r="K21" s="14" t="n"/>
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>Needs hosting access this agent doesn't have.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="23.25" customHeight="1" s="23">
       <c r="A22" s="11" t="inlineStr">
@@ -29019,11 +29083,15 @@
       <c r="H22" s="14" t="n"/>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="J22" s="16" t="n"/>
-      <c r="K22" s="14" t="n"/>
+      <c r="K22" s="14" t="inlineStr">
+        <is>
+          <t>Needs hosting access this agent doesn't have.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="34.5" customHeight="1" s="23">
       <c r="A23" s="17" t="inlineStr">
@@ -29064,11 +29132,15 @@
       <c r="H23" s="14" t="n"/>
       <c r="I23" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="J23" s="16" t="n"/>
-      <c r="K23" s="14" t="n"/>
+      <c r="K23" s="14" t="inlineStr">
+        <is>
+          <t>No analytics connector is attached in this workspace at all (confirmed - see CLAUDE.md capability matrix bucket 4). Needs a GA4 property created/shared and connected before this agent can do anything with it.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="34.5" customHeight="1" s="23">
       <c r="A24" s="11" t="inlineStr">
@@ -29109,11 +29181,15 @@
       <c r="H24" s="14" t="n"/>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J24" s="16" t="n"/>
-      <c r="K24" s="14" t="n"/>
+      <c r="K24" s="14" t="inlineStr">
+        <is>
+          <t>This item is about the live WordPress site, which has no persistent WhatsApp CTA. Side finding: the Next.js rebuild in this repo already has this (src/components/layout/WhatsAppFAB.tsx, rendered site-wide) - not a gap in the rebuild. Also: this row's evidence cites the WhatsApp number as +92 332 5017478, which differs from the phone number (+92 333 5010042) found in OFF-07's NAP data - confirm which number belongs where before using either as the source of truth for lib/constants.ts (ACTION-PLAN.md P0 NAP task).</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="23.25" customHeight="1" s="23">
       <c r="A25" s="17" t="inlineStr">
@@ -29154,11 +29230,15 @@
       <c r="H25" s="14" t="n"/>
       <c r="I25" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J25" s="16" t="n"/>
-      <c r="K25" s="14" t="n"/>
+      <c r="K25" s="14" t="inlineStr">
+        <is>
+          <t>Checked via site: search (2026-10-01) for the specific spam patterns named in the audit (/tag/smoking, /tag/gene-therapy, generic gambling/adult terms) - none currently appear in Google's index for this domain. Good sign, not authoritative - confirm against the Search Console Removals/Pages report directly before treating this as closed.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="23">
       <c r="A26" s="6" t="n"/>
@@ -56081,7 +56161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="23" min="1" max="1"/>
@@ -56305,6 +56385,43 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="150" customHeight="1" s="23">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>Technical SEO</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>All 20 rows (TECH-01 to TECH-20)</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>Reviewed every Technical SEO item (all still 'Not Started' after three weeks) and did everything remotely checkable without WordPress/hosting access, which this agent doesn't have for the live site.</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>Confirmed via site: search that the specific spam-era URLs (/tag/smoking, /tag/gene-therapy, gambling/adult terms) are no longer indexed, but tag and category archives in general still are (TECH-03/05/13/14/20). Diagnosed TECH-08's root cause precisely via GSC API (permission-level mismatch between the URL-prefix and domain properties). Confirmed TECH-04 (manual actions/security issues) has no API path - UI-only. Confirmed TECH-11/12 (robots.txt/sitemap) can't even be read remotely - this environment blocks fetching drranairfan.com directly. Found that TECH-19 (WhatsApp CTA) is already solved in the Next.js rebuild, and flagged a phone-number vs WhatsApp-number discrepancy worth resolving before the NAP fix. Wrote docs/seo/technical/TECH-runbook.md: an ordered, phase-by-phase checklist for whoever has WordPress/hosting/GSC-UI access to actually execute the 14 items this agent could not touch - starting with TECH-01 (the still-unverified backdoor) and TECH-02 (credential rotation), which should happen before anything else in this tracker, SEO or otherwise. 8 rows set to 'In Progress' with real findings; 12 set to 'Blocked' with the specific access gap named.</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>docs/seo/technical/TECH-runbook.md; Technical SEO tab, all 20 rows (Status + Notes)</t>
+        </is>
+      </c>
+      <c r="G10" s="32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>

--- a/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
+++ b/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
@@ -8,6 +8,7 @@
     <sheet name="Technical SEO" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Backlink Audit" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Completed Tasks" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="OP-02 Blog Audit" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'On Page SEO Issue'!$A$5:$K$25</definedName>
@@ -21,11 +22,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -87,6 +89,10 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="12">
@@ -192,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -281,6 +287,24 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -825,11 +849,15 @@
       <c r="H6" s="14" t="n"/>
       <c r="I6" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J6" s="16" t="n"/>
-      <c r="K6" s="14" t="n"/>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>Drafted ready-to-use byline/medical-reviewer content in docs/seo/content/OP-01-author-bio-boxes.md: a full bio box + short 'Medically reviewed by' line for Dr. Rana Irfan using only confirmed credentials (Immediate Past President ABHRS, FISHRS, 25+ years, real ABHRS/ISHRS/social profile links). Dr. Uzma Irfan's bio is a placeholder only - no confirmed individual credentials for her exist in this engagement, so it's deliberately not filled in. Actual site-wide application needs WordPress/Elementor access this agent doesn't have, and should happen after the OP-02 blog audit (no point bylining a page that's about to be merged/deleted).</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="34.5" customHeight="1" s="23">
       <c r="A7" s="17" t="inlineStr">
@@ -870,11 +898,15 @@
       <c r="H7" s="14" t="n"/>
       <c r="I7" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J7" s="16" t="n"/>
-      <c r="K7" s="14" t="n"/>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>Full data-backed audit done, not just the 5 examples in this row's Evidence: pulled Search Console page-level performance for every indexed URL with &gt;=1 impression in the last 90 days (250 URLs) and classified each into a content cluster with a recommended action - see the new 'OP-02 Blog Audit' tab in this workbook and docs/seo/content/OP-02-blog-audit-summary.md. Headline finding: the 'does X cause hair loss' drug/condition farm (52 URLs) out-clicks the clinic's own core service content (67 URLs) - 2,844 vs 2,206 clicks. Found 4 literal duplicate/near-duplicate pairs. Classification is this agent's analysis, not a final verdict - flagged a handful of rows as genuine judgment calls for someone who knows the actual patient questions. Before executing any 410: check each URL for inbound backlinks first (not yet done - needs a funded backlink tool or the Search Console Links report, see OFF-01).</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="45.75" customHeight="1" s="23">
       <c r="A8" s="11" t="inlineStr">
@@ -56161,7 +56193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="23" min="1" max="1"/>
@@ -56422,6 +56454,43 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="160" customHeight="1" s="23">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>On Page SEO Issue</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>OP-01, OP-02</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>Worked the two highest-leverage On-Page items: the E-E-A-T/byline gap tied to the April 2026 demotion, and the topical-authority-dilution blog content problem - with real data instead of the handful of examples already in the tracker.</t>
+        </is>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>OP-02: pulled Search Console page-level data for all 250 indexed URLs with impressions in the last 90 days, classified each into a content cluster (core/commercial, drug-interaction farm, styling/cosmetic off-topic, finasteride micro-pages, post-op care, dermatology/symptom, generic informational, duplicates, etc.) with a recommended action, and wrote it all into a new 'OP-02 Blog Audit' tab in this workbook plus a cluster-level summary in docs/seo/content/OP-02-blog-audit-summary.md. Found the drug/condition content farm (52 URLs, 2,844 clicks) actually out-clicks the clinic's own core service content (67 URLs, 2,206 clicks) - OP-02's dilution claim, now with numbers. Found 4 literal duplicate/near-duplicate URL pairs. OP-01: drafted a full author bio box + short reviewer byline for Dr. Rana Irfan using only confirmed credentials, in docs/seo/content/OP-01-author-bio-boxes.md - left Dr. Uzma Irfan's bio as an explicit placeholder since no individual credentials for her were confirmed this session. Neither change is live - OP-01 needs WordPress access to publish, and OP-02's classification needs a per-URL backlink check before any 410 is executed, plus someone at the clinic to confirm a handful of judgment-call rows.</t>
+        </is>
+      </c>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>docs/seo/content/OP-01-author-bio-boxes.md; docs/seo/content/OP-02-blog-audit-summary.md; DrRanaIrfanSEOIssueTracker.xlsx tab 'OP-02 Blog Audit' (new, 250 rows); On Page SEO Issue tab rows OP-01/OP-02</t>
+        </is>
+      </c>
+      <c r="G11" s="32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
@@ -56434,4 +56503,8149 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF1C3976"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J255"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="46" customWidth="1" style="23" min="1" max="1"/>
+    <col width="10" customWidth="1" style="23" min="2" max="2"/>
+    <col width="11" customWidth="1" style="23" min="3" max="3"/>
+    <col width="9" customWidth="1" style="23" min="4" max="4"/>
+    <col width="10" customWidth="1" style="23" min="5" max="5"/>
+    <col width="32" customWidth="1" style="23" min="6" max="6"/>
+    <col width="28" customWidth="1" style="23" min="7" max="7"/>
+    <col width="16" customWidth="1" style="23" min="8" max="8"/>
+    <col width="9" customWidth="1" style="23" min="9" max="9"/>
+    <col width="40" customWidth="1" style="23" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customHeight="1" s="23">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>OP-02 BLOG URL AUDIT  |  drranairfan.com  |  Source: Google Search Console page performance, 04 Jul - 01 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1" s="23">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>HOW TO USE:  Every indexed URL that had at least one impression in this window, classified into a content cluster with a recommended action. Cluster/Recommended Action is this agent's analysis - treat it as a strong starting point, not a final verdict, especially for borderline rows. Final Decision, Done? and Notes (yellow) are yours. Before any 410 (delete): check whether that URL has inbound backlinks first (see OFF-01/Backlink Audit) - 301 anything that does, 410 only what doesn't.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Total URLs</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>Total clicks (90d)</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Total impressions (90d)</t>
+        </is>
+      </c>
+      <c r="G3" s="28" t="inlineStr">
+        <is>
+          <t>Flagged for pruning/consolidation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="29">
+        <f>COUNTA($A$6:$A$1000)</f>
+        <v/>
+      </c>
+      <c r="C4" s="29">
+        <f>SUM($B$6:$B$1000)</f>
+        <v/>
+      </c>
+      <c r="E4" s="29">
+        <f>SUM($C$6:$C$1000)</f>
+        <v/>
+      </c>
+      <c r="G4" s="29">
+        <f>COUNTIF($G$6:$G$1000,"Prune*")+COUNTIF($G$6:$G$1000,"Consolidate*")+COUNTIF($G$6:$G$1000,"Merge*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" s="23">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>Clicks (90d)</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>Impressions (90d)</t>
+        </is>
+      </c>
+      <c r="D5" s="30" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="E5" s="30" t="inlineStr">
+        <is>
+          <t>Avg Position</t>
+        </is>
+      </c>
+      <c r="F5" s="30" t="inlineStr">
+        <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="G5" s="30" t="inlineStr">
+        <is>
+          <t>Recommended Action</t>
+        </is>
+      </c>
+      <c r="H5" s="30" t="inlineStr">
+        <is>
+          <t>Final Decision</t>
+        </is>
+      </c>
+      <c r="I5" s="30" t="inlineStr">
+        <is>
+          <t>Done?</t>
+        </is>
+      </c>
+      <c r="J5" s="30" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/how-to-stop-hair-growth-on-moles/</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="n">
+        <v>80</v>
+      </c>
+      <c r="C6" s="34" t="n">
+        <v>117938</v>
+      </c>
+      <c r="D6" s="35" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="E6" s="36" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="F6" s="33" t="inlineStr">
+        <is>
+          <t>Generic informational (off-topic/zero-click)</t>
+        </is>
+      </c>
+      <c r="G6" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H6" s="38" t="n"/>
+      <c r="I6" s="38" t="n"/>
+      <c r="J6" s="38" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/best-haircuts-for-thin-hair/</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="n">
+        <v>189</v>
+      </c>
+      <c r="C7" s="34" t="n">
+        <v>117801</v>
+      </c>
+      <c r="D7" s="35" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="E7" s="36" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="F7" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G7" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H7" s="38" t="n"/>
+      <c r="I7" s="38" t="n"/>
+      <c r="J7" s="38" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/mans-shaved-head-to-grow-back/</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="n">
+        <v>146</v>
+      </c>
+      <c r="C8" s="34" t="n">
+        <v>61656</v>
+      </c>
+      <c r="D8" s="35" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E8" s="36" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="F8" s="33" t="inlineStr">
+        <is>
+          <t>Generic informational (off-topic/zero-click)</t>
+        </is>
+      </c>
+      <c r="G8" s="37" t="inlineStr">
+        <is>
+          <t>Prune or rework to link to services</t>
+        </is>
+      </c>
+      <c r="H8" s="38" t="n"/>
+      <c r="I8" s="38" t="n"/>
+      <c r="J8" s="38" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/what-is-the-big-3-for-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="n">
+        <v>103</v>
+      </c>
+      <c r="C9" s="34" t="n">
+        <v>59008</v>
+      </c>
+      <c r="D9" s="35" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="E9" s="36" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="F9" s="33" t="inlineStr">
+        <is>
+          <t>Generic informational (off-topic/zero-click)</t>
+        </is>
+      </c>
+      <c r="G9" s="37" t="inlineStr">
+        <is>
+          <t>Rework into the clinic's own protocol page rather than delete</t>
+        </is>
+      </c>
+      <c r="H9" s="38" t="n"/>
+      <c r="I9" s="38" t="n"/>
+      <c r="J9" s="38" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/white-stuff-in-hair-not-dandruff/</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="C10" s="34" t="n">
+        <v>36566</v>
+      </c>
+      <c r="D10" s="35" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="E10" s="36" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>Dermatology/symptom content (tangential)</t>
+        </is>
+      </c>
+      <c r="G10" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate - low priority</t>
+        </is>
+      </c>
+      <c r="H10" s="38" t="n"/>
+      <c r="I10" s="38" t="n"/>
+      <c r="J10" s="38" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/finasteride-for-diffuse-thinning/</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="n">
+        <v>42</v>
+      </c>
+      <c r="C11" s="34" t="n">
+        <v>28859</v>
+      </c>
+      <c r="D11" s="35" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="E11" s="36" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G11" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H11" s="38" t="n"/>
+      <c r="I11" s="38" t="n"/>
+      <c r="J11" s="38" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/do-people-with-curly-hair-go-bald/</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="n">
+        <v>70</v>
+      </c>
+      <c r="C12" s="34" t="n">
+        <v>28813</v>
+      </c>
+      <c r="D12" s="35" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E12" s="36" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G12" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H12" s="38" t="n"/>
+      <c r="I12" s="38" t="n"/>
+      <c r="J12" s="38" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-types-explained/</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="n">
+        <v>90</v>
+      </c>
+      <c r="C13" s="34" t="n">
+        <v>28641</v>
+      </c>
+      <c r="D13" s="35" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="E13" s="36" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G13" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H13" s="38" t="n"/>
+      <c r="I13" s="38" t="n"/>
+      <c r="J13" s="38" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-hair-weigh-anything/</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="n">
+        <v>36</v>
+      </c>
+      <c r="C14" s="34" t="n">
+        <v>27897</v>
+      </c>
+      <c r="D14" s="35" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="E14" s="36" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G14" s="37" t="inlineStr">
+        <is>
+          <t>Merge/301</t>
+        </is>
+      </c>
+      <c r="H14" s="38" t="n"/>
+      <c r="I14" s="38" t="n"/>
+      <c r="J14" s="38" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/white-piedra-vs-black-piedra/</t>
+        </is>
+      </c>
+      <c r="B15" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" s="34" t="n">
+        <v>27402</v>
+      </c>
+      <c r="D15" s="35" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="E15" s="36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>Dermatology/symptom content (tangential)</t>
+        </is>
+      </c>
+      <c r="G15" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate - low priority</t>
+        </is>
+      </c>
+      <c r="H15" s="38" t="n"/>
+      <c r="I15" s="38" t="n"/>
+      <c r="J15" s="38" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-plucking-cause-ingrown-hairs/</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="n">
+        <v>25</v>
+      </c>
+      <c r="C16" s="34" t="n">
+        <v>23444</v>
+      </c>
+      <c r="D16" s="35" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="E16" s="36" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="F16" s="33" t="inlineStr">
+        <is>
+          <t>Facial/skincare (adjacent vertical)</t>
+        </is>
+      </c>
+      <c r="G16" s="37" t="inlineStr">
+        <is>
+          <t>Business decision: keep as its own section if the clinic offers these, else prune</t>
+        </is>
+      </c>
+      <c r="H16" s="38" t="n"/>
+      <c r="I16" s="38" t="n"/>
+      <c r="J16" s="38" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/updated-hair-transplant-prices-in-pakistan/</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="n">
+        <v>214</v>
+      </c>
+      <c r="C17" s="34" t="n">
+        <v>22878</v>
+      </c>
+      <c r="D17" s="35" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="E17" s="36" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="F17" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G17" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H17" s="38" t="n"/>
+      <c r="I17" s="38" t="n"/>
+      <c r="J17" s="38" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/best-hair-color-for-men-without-side-effects/</t>
+        </is>
+      </c>
+      <c r="B18" s="34" t="n">
+        <v>259</v>
+      </c>
+      <c r="C18" s="34" t="n">
+        <v>20368</v>
+      </c>
+      <c r="D18" s="35" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="E18" s="36" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="F18" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G18" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H18" s="38" t="n"/>
+      <c r="I18" s="38" t="n"/>
+      <c r="J18" s="38" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/what-is-the-function-of-hair-on-the-body/</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="n">
+        <v>22</v>
+      </c>
+      <c r="C19" s="34" t="n">
+        <v>19395</v>
+      </c>
+      <c r="D19" s="35" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="E19" s="36" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="F19" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G19" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H19" s="38" t="n"/>
+      <c r="I19" s="38" t="n"/>
+      <c r="J19" s="38" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/how-much-does-hair-weigh/</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="n">
+        <v>48</v>
+      </c>
+      <c r="C20" s="34" t="n">
+        <v>18060</v>
+      </c>
+      <c r="D20" s="35" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="E20" s="36" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="F20" s="33" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G20" s="37" t="inlineStr">
+        <is>
+          <t>Merge/301</t>
+        </is>
+      </c>
+      <c r="H20" s="38" t="n"/>
+      <c r="I20" s="38" t="n"/>
+      <c r="J20" s="38" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/priorin-tablets-side-effects/</t>
+        </is>
+      </c>
+      <c r="B21" s="34" t="n">
+        <v>161</v>
+      </c>
+      <c r="C21" s="34" t="n">
+        <v>18041</v>
+      </c>
+      <c r="D21" s="35" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="E21" s="36" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="F21" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G21" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate or prune</t>
+        </is>
+      </c>
+      <c r="H21" s="38" t="n"/>
+      <c r="I21" s="38" t="n"/>
+      <c r="J21" s="38" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-prp-price-in-pakistan/</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="n">
+        <v>130</v>
+      </c>
+      <c r="C22" s="34" t="n">
+        <v>17373</v>
+      </c>
+      <c r="D22" s="35" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="E22" s="36" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F22" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G22" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H22" s="38" t="n"/>
+      <c r="I22" s="38" t="n"/>
+      <c r="J22" s="38" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/</t>
+        </is>
+      </c>
+      <c r="B23" s="34" t="n">
+        <v>524</v>
+      </c>
+      <c r="C23" s="34" t="n">
+        <v>16965</v>
+      </c>
+      <c r="D23" s="35" t="n">
+        <v>0.0309</v>
+      </c>
+      <c r="E23" s="36" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="F23" s="33" t="inlineStr">
+        <is>
+          <t>Core site page</t>
+        </is>
+      </c>
+      <c r="G23" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H23" s="38" t="n"/>
+      <c r="I23" s="38" t="n"/>
+      <c r="J23" s="38" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-hair-grow-back-after-thinning/</t>
+        </is>
+      </c>
+      <c r="B24" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="34" t="n">
+        <v>16669</v>
+      </c>
+      <c r="D24" s="35" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="E24" s="36" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="F24" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G24" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H24" s="38" t="n"/>
+      <c r="I24" s="38" t="n"/>
+      <c r="J24" s="38" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/tag/smoking/</t>
+        </is>
+      </c>
+      <c r="B25" s="34" t="n">
+        <v>3675</v>
+      </c>
+      <c r="C25" s="34" t="n">
+        <v>15746</v>
+      </c>
+      <c r="D25" s="35" t="n">
+        <v>0.2334</v>
+      </c>
+      <c r="E25" s="36" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="F25" s="33" t="inlineStr">
+        <is>
+          <t>Thin archive/technical</t>
+        </is>
+      </c>
+      <c r="G25" s="37" t="inlineStr">
+        <is>
+          <t>See TECH-03/14 — fix via noindex, not a content decision</t>
+        </is>
+      </c>
+      <c r="H25" s="38" t="n"/>
+      <c r="I25" s="38" t="n"/>
+      <c r="J25" s="38" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/is-buzz-cut-haram/</t>
+        </is>
+      </c>
+      <c r="B26" s="34" t="n">
+        <v>97</v>
+      </c>
+      <c r="C26" s="34" t="n">
+        <v>12671</v>
+      </c>
+      <c r="D26" s="35" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="E26" s="36" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="F26" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G26" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H26" s="38" t="n"/>
+      <c r="I26" s="38" t="n"/>
+      <c r="J26" s="38" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-we-cut-hair-on-periods/</t>
+        </is>
+      </c>
+      <c r="B27" s="34" t="n">
+        <v>156</v>
+      </c>
+      <c r="C27" s="34" t="n">
+        <v>12628</v>
+      </c>
+      <c r="D27" s="35" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="E27" s="36" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="F27" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G27" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H27" s="38" t="n"/>
+      <c r="I27" s="38" t="n"/>
+      <c r="J27" s="38" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/white-in-hair-follicles/</t>
+        </is>
+      </c>
+      <c r="B28" s="34" t="n">
+        <v>14</v>
+      </c>
+      <c r="C28" s="34" t="n">
+        <v>11820</v>
+      </c>
+      <c r="D28" s="35" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="E28" s="36" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="F28" s="33" t="inlineStr">
+        <is>
+          <t>Dermatology/symptom content (tangential)</t>
+        </is>
+      </c>
+      <c r="G28" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate - low priority</t>
+        </is>
+      </c>
+      <c r="H28" s="38" t="n"/>
+      <c r="I28" s="38" t="n"/>
+      <c r="J28" s="38" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/people-cut-their-hair-when-they-have-cancer/</t>
+        </is>
+      </c>
+      <c r="B29" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" s="34" t="n">
+        <v>11717</v>
+      </c>
+      <c r="D29" s="35" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="E29" s="36" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F29" s="33" t="inlineStr">
+        <is>
+          <t>Cancer/chemo hair loss</t>
+        </is>
+      </c>
+      <c r="G29" s="37" t="inlineStr">
+        <is>
+          <t>Low-priority keep (adjacent audience, not core)</t>
+        </is>
+      </c>
+      <c r="H29" s="38" t="n"/>
+      <c r="I29" s="38" t="n"/>
+      <c r="J29" s="38" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/cortisone-shot-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B30" s="34" t="n">
+        <v>1562</v>
+      </c>
+      <c r="C30" s="34" t="n">
+        <v>11457</v>
+      </c>
+      <c r="D30" s="35" t="n">
+        <v>0.1363</v>
+      </c>
+      <c r="E30" s="36" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="F30" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G30" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H30" s="38" t="n"/>
+      <c r="I30" s="38" t="n"/>
+      <c r="J30" s="38" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/graft-calculator/</t>
+        </is>
+      </c>
+      <c r="B31" s="34" t="n">
+        <v>1065</v>
+      </c>
+      <c r="C31" s="34" t="n">
+        <v>10524</v>
+      </c>
+      <c r="D31" s="35" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="E31" s="36" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="F31" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G31" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H31" s="38" t="n"/>
+      <c r="I31" s="38" t="n"/>
+      <c r="J31" s="38" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/side-effects-of-plucking-facial-hair/</t>
+        </is>
+      </c>
+      <c r="B32" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" s="34" t="n">
+        <v>10242</v>
+      </c>
+      <c r="D32" s="35" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="E32" s="36" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="F32" s="33" t="inlineStr">
+        <is>
+          <t>Facial/skincare (adjacent vertical)</t>
+        </is>
+      </c>
+      <c r="G32" s="37" t="inlineStr">
+        <is>
+          <t>Business decision: keep as its own section if the clinic offers these, else prune</t>
+        </is>
+      </c>
+      <c r="H32" s="38" t="n"/>
+      <c r="I32" s="38" t="n"/>
+      <c r="J32" s="38" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/best-hair-cream-for-beard/</t>
+        </is>
+      </c>
+      <c r="B33" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="C33" s="34" t="n">
+        <v>10132</v>
+      </c>
+      <c r="D33" s="35" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="E33" s="36" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="F33" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G33" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H33" s="38" t="n"/>
+      <c r="I33" s="38" t="n"/>
+      <c r="J33" s="38" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-having-longer-hair-make-it-thinner/</t>
+        </is>
+      </c>
+      <c r="B34" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="C34" s="34" t="n">
+        <v>9577</v>
+      </c>
+      <c r="D34" s="35" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="E34" s="36" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="F34" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G34" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H34" s="38" t="n"/>
+      <c r="I34" s="38" t="n"/>
+      <c r="J34" s="38" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/trichodynia-scalp-pain/</t>
+        </is>
+      </c>
+      <c r="B35" s="34" t="n">
+        <v>24</v>
+      </c>
+      <c r="C35" s="34" t="n">
+        <v>9401</v>
+      </c>
+      <c r="D35" s="35" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="E35" s="36" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="F35" s="33" t="inlineStr">
+        <is>
+          <t>Dermatology/symptom content (tangential)</t>
+        </is>
+      </c>
+      <c r="G35" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate - low priority</t>
+        </is>
+      </c>
+      <c r="H35" s="38" t="n"/>
+      <c r="I35" s="38" t="n"/>
+      <c r="J35" s="38" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/understanding-the-scalp-muscle/</t>
+        </is>
+      </c>
+      <c r="B36" s="34" t="n">
+        <v>92</v>
+      </c>
+      <c r="C36" s="34" t="n">
+        <v>8818</v>
+      </c>
+      <c r="D36" s="35" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="E36" s="36" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="F36" s="33" t="inlineStr">
+        <is>
+          <t>Generic informational (off-topic/zero-click)</t>
+        </is>
+      </c>
+      <c r="G36" s="37" t="inlineStr">
+        <is>
+          <t>Prune or merge into a shorter FAQ</t>
+        </is>
+      </c>
+      <c r="H36" s="38" t="n"/>
+      <c r="I36" s="38" t="n"/>
+      <c r="J36" s="38" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-minoxidil-work-without-finasteride/</t>
+        </is>
+      </c>
+      <c r="B37" s="34" t="n">
+        <v>87</v>
+      </c>
+      <c r="C37" s="34" t="n">
+        <v>8818</v>
+      </c>
+      <c r="D37" s="35" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="E37" s="36" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="F37" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G37" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H37" s="38" t="n"/>
+      <c r="I37" s="38" t="n"/>
+      <c r="J37" s="38" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/mold-in-hair-symptoms/</t>
+        </is>
+      </c>
+      <c r="B38" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C38" s="34" t="n">
+        <v>8508</v>
+      </c>
+      <c r="D38" s="35" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="E38" s="36" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="F38" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G38" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H38" s="38" t="n"/>
+      <c r="I38" s="38" t="n"/>
+      <c r="J38" s="38" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/why-do-people-with-curly-hair-experience-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B39" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" s="34" t="n">
+        <v>8274</v>
+      </c>
+      <c r="D39" s="35" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="E39" s="36" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="F39" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G39" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H39" s="38" t="n"/>
+      <c r="I39" s="38" t="n"/>
+      <c r="J39" s="38" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/tag/gene-therapy/</t>
+        </is>
+      </c>
+      <c r="B40" s="34" t="n">
+        <v>3497</v>
+      </c>
+      <c r="C40" s="34" t="n">
+        <v>8174</v>
+      </c>
+      <c r="D40" s="35" t="n">
+        <v>0.4278</v>
+      </c>
+      <c r="E40" s="36" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="F40" s="33" t="inlineStr">
+        <is>
+          <t>Thin archive/technical</t>
+        </is>
+      </c>
+      <c r="G40" s="37" t="inlineStr">
+        <is>
+          <t>See TECH-03/14 — fix via noindex, not a content decision</t>
+        </is>
+      </c>
+      <c r="H40" s="38" t="n"/>
+      <c r="I40" s="38" t="n"/>
+      <c r="J40" s="38" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/do-antibiotics-affect-hair-coloring/</t>
+        </is>
+      </c>
+      <c r="B41" s="34" t="n">
+        <v>293</v>
+      </c>
+      <c r="C41" s="34" t="n">
+        <v>8013</v>
+      </c>
+      <c r="D41" s="35" t="n">
+        <v>0.0366</v>
+      </c>
+      <c r="E41" s="36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F41" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G41" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H41" s="38" t="n"/>
+      <c r="I41" s="38" t="n"/>
+      <c r="J41" s="38" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-garnier-fructis-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B42" s="34" t="n">
+        <v>93</v>
+      </c>
+      <c r="C42" s="34" t="n">
+        <v>7938</v>
+      </c>
+      <c r="D42" s="35" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="E42" s="36" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="F42" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G42" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H42" s="38" t="n"/>
+      <c r="I42" s="38" t="n"/>
+      <c r="J42" s="38" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/is-it-normal-for-hair-to-itch-when-growing-back/</t>
+        </is>
+      </c>
+      <c r="B43" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="C43" s="34" t="n">
+        <v>7908</v>
+      </c>
+      <c r="D43" s="35" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="E43" s="36" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="F43" s="33" t="inlineStr">
+        <is>
+          <t>Cancer/chemo hair loss</t>
+        </is>
+      </c>
+      <c r="G43" s="37" t="inlineStr">
+        <is>
+          <t>Low-priority keep (adjacent audience, not core)</t>
+        </is>
+      </c>
+      <c r="H43" s="38" t="n"/>
+      <c r="I43" s="38" t="n"/>
+      <c r="J43" s="38" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/how-many-hair-strands-do-we-have/</t>
+        </is>
+      </c>
+      <c r="B44" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" s="34" t="n">
+        <v>7878</v>
+      </c>
+      <c r="D44" s="35" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="E44" s="36" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="F44" s="33" t="inlineStr">
+        <is>
+          <t>Generic informational (off-topic/zero-click)</t>
+        </is>
+      </c>
+      <c r="G44" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H44" s="38" t="n"/>
+      <c r="I44" s="38" t="n"/>
+      <c r="J44" s="38" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/foods-that-increase-dht-production/</t>
+        </is>
+      </c>
+      <c r="B45" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="C45" s="34" t="n">
+        <v>7836</v>
+      </c>
+      <c r="D45" s="35" t="n">
+        <v>0.008200000000000001</v>
+      </c>
+      <c r="E45" s="36" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="F45" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G45" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H45" s="38" t="n"/>
+      <c r="I45" s="38" t="n"/>
+      <c r="J45" s="38" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-finasteride-affect-beard-growth/</t>
+        </is>
+      </c>
+      <c r="B46" s="34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C46" s="34" t="n">
+        <v>7233</v>
+      </c>
+      <c r="D46" s="35" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="E46" s="36" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="F46" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G46" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H46" s="38" t="n"/>
+      <c r="I46" s="38" t="n"/>
+      <c r="J46" s="38" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/scalp-exercises-expert-guide/scalp-stretching-exercises/</t>
+        </is>
+      </c>
+      <c r="B47" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="C47" s="34" t="n">
+        <v>6893</v>
+      </c>
+      <c r="D47" s="35" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="E47" s="36" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="F47" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G47" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H47" s="38" t="n"/>
+      <c r="I47" s="38" t="n"/>
+      <c r="J47" s="38" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/scalp-exercises-expert-guide/scalp-tingling-during-exercise/</t>
+        </is>
+      </c>
+      <c r="B48" s="34" t="n">
+        <v>69</v>
+      </c>
+      <c r="C48" s="34" t="n">
+        <v>6387</v>
+      </c>
+      <c r="D48" s="35" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="E48" s="36" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="F48" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G48" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H48" s="38" t="n"/>
+      <c r="I48" s="38" t="n"/>
+      <c r="J48" s="38" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-liver-damage-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B49" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="C49" s="34" t="n">
+        <v>6130</v>
+      </c>
+      <c r="D49" s="35" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="E49" s="36" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F49" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G49" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H49" s="38" t="n"/>
+      <c r="I49" s="38" t="n"/>
+      <c r="J49" s="38" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/ferritin-and-hair-fall/</t>
+        </is>
+      </c>
+      <c r="B50" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C50" s="34" t="n">
+        <v>6122</v>
+      </c>
+      <c r="D50" s="35" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="E50" s="36" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="F50" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G50" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H50" s="38" t="n"/>
+      <c r="I50" s="38" t="n"/>
+      <c r="J50" s="38" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/creatine-and-finasteride/</t>
+        </is>
+      </c>
+      <c r="B51" s="34" t="n">
+        <v>37</v>
+      </c>
+      <c r="C51" s="34" t="n">
+        <v>6079</v>
+      </c>
+      <c r="D51" s="35" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="E51" s="36" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="F51" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G51" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H51" s="38" t="n"/>
+      <c r="I51" s="38" t="n"/>
+      <c r="J51" s="38" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/doxycycline-hair-thinning/</t>
+        </is>
+      </c>
+      <c r="B52" s="34" t="n">
+        <v>54</v>
+      </c>
+      <c r="C52" s="34" t="n">
+        <v>6063</v>
+      </c>
+      <c r="D52" s="35" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="E52" s="36" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="F52" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G52" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H52" s="38" t="n"/>
+      <c r="I52" s="38" t="n"/>
+      <c r="J52" s="38" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/scalp-exercises-expert-guide/scalp-stitches-and-exercise/</t>
+        </is>
+      </c>
+      <c r="B53" s="34" t="n">
+        <v>81</v>
+      </c>
+      <c r="C53" s="34" t="n">
+        <v>5960</v>
+      </c>
+      <c r="D53" s="35" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="E53" s="36" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="F53" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G53" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H53" s="38" t="n"/>
+      <c r="I53" s="38" t="n"/>
+      <c r="J53" s="38" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hims-vs-nutrafol/</t>
+        </is>
+      </c>
+      <c r="B54" s="34" t="n">
+        <v>78</v>
+      </c>
+      <c r="C54" s="34" t="n">
+        <v>5834</v>
+      </c>
+      <c r="D54" s="35" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="E54" s="36" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="F54" s="33" t="inlineStr">
+        <is>
+          <t>Competitor-brand comparison (risky)</t>
+        </is>
+      </c>
+      <c r="G54" s="37" t="inlineStr">
+        <is>
+          <t>Prune or rework to feature the clinic's own offering</t>
+        </is>
+      </c>
+      <c r="H54" s="38" t="n"/>
+      <c r="I54" s="38" t="n"/>
+      <c r="J54" s="38" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/worst-steroids-for-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B55" s="34" t="n">
+        <v>156</v>
+      </c>
+      <c r="C55" s="34" t="n">
+        <v>5796</v>
+      </c>
+      <c r="D55" s="35" t="n">
+        <v>0.0269</v>
+      </c>
+      <c r="E55" s="36" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="F55" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G55" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H55" s="38" t="n"/>
+      <c r="I55" s="38" t="n"/>
+      <c r="J55" s="38" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/black-hair-types/</t>
+        </is>
+      </c>
+      <c r="B56" s="34" t="n">
+        <v>49</v>
+      </c>
+      <c r="C56" s="34" t="n">
+        <v>5325</v>
+      </c>
+      <c r="D56" s="35" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="E56" s="36" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="F56" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G56" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H56" s="38" t="n"/>
+      <c r="I56" s="38" t="n"/>
+      <c r="J56" s="38" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-finasteride-cause-heart-palpitations/</t>
+        </is>
+      </c>
+      <c r="B57" s="34" t="n">
+        <v>80</v>
+      </c>
+      <c r="C57" s="34" t="n">
+        <v>5037</v>
+      </c>
+      <c r="D57" s="35" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="E57" s="36" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="F57" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G57" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H57" s="38" t="n"/>
+      <c r="I57" s="38" t="n"/>
+      <c r="J57" s="38" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/1a-hair-vs-1b/</t>
+        </is>
+      </c>
+      <c r="B58" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" s="34" t="n">
+        <v>4839</v>
+      </c>
+      <c r="D58" s="35" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E58" s="36" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="F58" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G58" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H58" s="38" t="n"/>
+      <c r="I58" s="38" t="n"/>
+      <c r="J58" s="38" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-blood-donation-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B59" s="34" t="n">
+        <v>83</v>
+      </c>
+      <c r="C59" s="34" t="n">
+        <v>4794</v>
+      </c>
+      <c r="D59" s="35" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="E59" s="36" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="F59" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G59" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H59" s="38" t="n"/>
+      <c r="I59" s="38" t="n"/>
+      <c r="J59" s="38" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-a-urine-infection-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B60" s="34" t="n">
+        <v>78</v>
+      </c>
+      <c r="C60" s="34" t="n">
+        <v>4741</v>
+      </c>
+      <c r="D60" s="35" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="E60" s="36" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="F60" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G60" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H60" s="38" t="n"/>
+      <c r="I60" s="38" t="n"/>
+      <c r="J60" s="38" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/what-is-the-hair/</t>
+        </is>
+      </c>
+      <c r="B61" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="C61" s="34" t="n">
+        <v>4734</v>
+      </c>
+      <c r="D61" s="35" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="E61" s="36" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="F61" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G61" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H61" s="38" t="n"/>
+      <c r="I61" s="38" t="n"/>
+      <c r="J61" s="38" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-cost-in-pakistan/</t>
+        </is>
+      </c>
+      <c r="B62" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="C62" s="34" t="n">
+        <v>4671</v>
+      </c>
+      <c r="D62" s="35" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="E62" s="36" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="F62" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G62" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H62" s="38" t="n"/>
+      <c r="I62" s="38" t="n"/>
+      <c r="J62" s="38" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/eyebrows-with-white-hair/</t>
+        </is>
+      </c>
+      <c r="B63" s="34" t="n">
+        <v>34</v>
+      </c>
+      <c r="C63" s="34" t="n">
+        <v>4650</v>
+      </c>
+      <c r="D63" s="35" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="E63" s="36" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="F63" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G63" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H63" s="38" t="n"/>
+      <c r="I63" s="38" t="n"/>
+      <c r="J63" s="38" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-combing-wet-hair-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B64" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="C64" s="34" t="n">
+        <v>4623</v>
+      </c>
+      <c r="D64" s="35" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E64" s="36" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="F64" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G64" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H64" s="38" t="n"/>
+      <c r="I64" s="38" t="n"/>
+      <c r="J64" s="38" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/scalp-exercises-expert-guide/scalp-tension-exercises/</t>
+        </is>
+      </c>
+      <c r="B65" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C65" s="34" t="n">
+        <v>4582</v>
+      </c>
+      <c r="D65" s="35" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="E65" s="36" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="F65" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G65" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H65" s="38" t="n"/>
+      <c r="I65" s="38" t="n"/>
+      <c r="J65" s="38" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/how-long-does-hair-loss-from-antibiotics-last/</t>
+        </is>
+      </c>
+      <c r="B66" s="34" t="n">
+        <v>36</v>
+      </c>
+      <c r="C66" s="34" t="n">
+        <v>4555</v>
+      </c>
+      <c r="D66" s="35" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="E66" s="36" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="F66" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G66" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub</t>
+        </is>
+      </c>
+      <c r="H66" s="38" t="n"/>
+      <c r="I66" s="38" t="n"/>
+      <c r="J66" s="38" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/finasteride-for-bodybuilding/</t>
+        </is>
+      </c>
+      <c r="B67" s="34" t="n">
+        <v>42</v>
+      </c>
+      <c r="C67" s="34" t="n">
+        <v>4551</v>
+      </c>
+      <c r="D67" s="35" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="E67" s="36" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="F67" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G67" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H67" s="38" t="n"/>
+      <c r="I67" s="38" t="n"/>
+      <c r="J67" s="38" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/category/facial/</t>
+        </is>
+      </c>
+      <c r="B68" s="34" t="n">
+        <v>1372</v>
+      </c>
+      <c r="C68" s="34" t="n">
+        <v>4084</v>
+      </c>
+      <c r="D68" s="35" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="E68" s="36" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="F68" s="33" t="inlineStr">
+        <is>
+          <t>Thin archive/technical</t>
+        </is>
+      </c>
+      <c r="G68" s="37" t="inlineStr">
+        <is>
+          <t>See TECH-03/14 — fix via noindex, not a content decision</t>
+        </is>
+      </c>
+      <c r="H68" s="38" t="n"/>
+      <c r="I68" s="38" t="n"/>
+      <c r="J68" s="38" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/foods-that-increase-dht/</t>
+        </is>
+      </c>
+      <c r="B69" s="34" t="n">
+        <v>23</v>
+      </c>
+      <c r="C69" s="34" t="n">
+        <v>4065</v>
+      </c>
+      <c r="D69" s="35" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="E69" s="36" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="F69" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G69" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into a single DHT/diet FAQ section</t>
+        </is>
+      </c>
+      <c r="H69" s="38" t="n"/>
+      <c r="I69" s="38" t="n"/>
+      <c r="J69" s="38" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-you-take-nutrafol-and-finasteride-together/</t>
+        </is>
+      </c>
+      <c r="B70" s="34" t="n">
+        <v>120</v>
+      </c>
+      <c r="C70" s="34" t="n">
+        <v>4027</v>
+      </c>
+      <c r="D70" s="35" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="E70" s="36" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="F70" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G70" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H70" s="38" t="n"/>
+      <c r="I70" s="38" t="n"/>
+      <c r="J70" s="38" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/paresthesia-of-the-scalp/</t>
+        </is>
+      </c>
+      <c r="B71" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="C71" s="34" t="n">
+        <v>3945</v>
+      </c>
+      <c r="D71" s="35" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="E71" s="36" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="F71" s="33" t="inlineStr">
+        <is>
+          <t>Dermatology/symptom content (tangential)</t>
+        </is>
+      </c>
+      <c r="G71" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate - low priority</t>
+        </is>
+      </c>
+      <c r="H71" s="38" t="n"/>
+      <c r="I71" s="38" t="n"/>
+      <c r="J71" s="38" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-zyn-cause-hair-loss-2/</t>
+        </is>
+      </c>
+      <c r="B72" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="C72" s="34" t="n">
+        <v>3918</v>
+      </c>
+      <c r="D72" s="35" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="E72" s="36" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="F72" s="33" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G72" s="37" t="inlineStr">
+        <is>
+          <t>Merge/301</t>
+        </is>
+      </c>
+      <c r="H72" s="38" t="n"/>
+      <c r="I72" s="38" t="n"/>
+      <c r="J72" s="38" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/finasteride-for-facial-hair/</t>
+        </is>
+      </c>
+      <c r="B73" s="34" t="n">
+        <v>900</v>
+      </c>
+      <c r="C73" s="34" t="n">
+        <v>3899</v>
+      </c>
+      <c r="D73" s="35" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="E73" s="36" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="F73" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G73" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H73" s="38" t="n"/>
+      <c r="I73" s="38" t="n"/>
+      <c r="J73" s="38" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-follicle-structure/</t>
+        </is>
+      </c>
+      <c r="B74" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="C74" s="34" t="n">
+        <v>3896</v>
+      </c>
+      <c r="D74" s="35" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="E74" s="36" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F74" s="33" t="inlineStr">
+        <is>
+          <t>Generic informational (off-topic/zero-click)</t>
+        </is>
+      </c>
+      <c r="G74" s="37" t="inlineStr">
+        <is>
+          <t>Fold into a procedure page as background, not standalone</t>
+        </is>
+      </c>
+      <c r="H74" s="38" t="n"/>
+      <c r="I74" s="38" t="n"/>
+      <c r="J74" s="38" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-milk-increase-dht/</t>
+        </is>
+      </c>
+      <c r="B75" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="C75" s="34" t="n">
+        <v>3865</v>
+      </c>
+      <c r="D75" s="35" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="E75" s="36" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="F75" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G75" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into a single DHT/diet FAQ section</t>
+        </is>
+      </c>
+      <c r="H75" s="38" t="n"/>
+      <c r="I75" s="38" t="n"/>
+      <c r="J75" s="38" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/finasteride-and-minoxidil-tablets/</t>
+        </is>
+      </c>
+      <c r="B76" s="34" t="n">
+        <v>83</v>
+      </c>
+      <c r="C76" s="34" t="n">
+        <v>3734</v>
+      </c>
+      <c r="D76" s="35" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="E76" s="36" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="F76" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G76" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H76" s="38" t="n"/>
+      <c r="I76" s="38" t="n"/>
+      <c r="J76" s="38" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/pros-and-cons-of-long-hair/</t>
+        </is>
+      </c>
+      <c r="B77" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="C77" s="34" t="n">
+        <v>3715</v>
+      </c>
+      <c r="D77" s="35" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E77" s="36" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="F77" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G77" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H77" s="38" t="n"/>
+      <c r="I77" s="38" t="n"/>
+      <c r="J77" s="38" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/flow-mens-hair/</t>
+        </is>
+      </c>
+      <c r="B78" s="34" t="n">
+        <v>36</v>
+      </c>
+      <c r="C78" s="34" t="n">
+        <v>3693</v>
+      </c>
+      <c r="D78" s="35" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="E78" s="36" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="F78" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G78" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H78" s="38" t="n"/>
+      <c r="I78" s="38" t="n"/>
+      <c r="J78" s="38" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-extensions-prices-in-pakistan/</t>
+        </is>
+      </c>
+      <c r="B79" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="C79" s="34" t="n">
+        <v>3530</v>
+      </c>
+      <c r="D79" s="35" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="E79" s="36" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F79" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G79" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H79" s="38" t="n"/>
+      <c r="I79" s="38" t="n"/>
+      <c r="J79" s="38" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/natural-alternatives-to-finasteride/</t>
+        </is>
+      </c>
+      <c r="B80" s="34" t="n">
+        <v>15</v>
+      </c>
+      <c r="C80" s="34" t="n">
+        <v>3501</v>
+      </c>
+      <c r="D80" s="35" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="E80" s="36" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="F80" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G80" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H80" s="38" t="n"/>
+      <c r="I80" s="38" t="n"/>
+      <c r="J80" s="38" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/why-your-hair-stings/</t>
+        </is>
+      </c>
+      <c r="B81" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C81" s="34" t="n">
+        <v>3475</v>
+      </c>
+      <c r="D81" s="35" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="E81" s="36" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="F81" s="33" t="inlineStr">
+        <is>
+          <t>Dermatology/symptom content (tangential)</t>
+        </is>
+      </c>
+      <c r="G81" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate - low priority</t>
+        </is>
+      </c>
+      <c r="H81" s="38" t="n"/>
+      <c r="I81" s="38" t="n"/>
+      <c r="J81" s="38" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-cost-in-pakistan/hair-transplant-cost-in-lahore-pakistan/</t>
+        </is>
+      </c>
+      <c r="B82" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C82" s="34" t="n">
+        <v>3438</v>
+      </c>
+      <c r="D82" s="35" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="E82" s="36" t="n">
+        <v>59.54</v>
+      </c>
+      <c r="F82" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G82" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H82" s="38" t="n"/>
+      <c r="I82" s="38" t="n"/>
+      <c r="J82" s="38" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-specialist-in-rawalpindi-dr-rana-irfan/</t>
+        </is>
+      </c>
+      <c r="B83" s="34" t="n">
+        <v>39</v>
+      </c>
+      <c r="C83" s="34" t="n">
+        <v>3416</v>
+      </c>
+      <c r="D83" s="35" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="E83" s="36" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="F83" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G83" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H83" s="38" t="n"/>
+      <c r="I83" s="38" t="n"/>
+      <c r="J83" s="38" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/bald-spots-in-curly-hair/</t>
+        </is>
+      </c>
+      <c r="B84" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C84" s="34" t="n">
+        <v>3372</v>
+      </c>
+      <c r="D84" s="35" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="E84" s="36" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="F84" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G84" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H84" s="38" t="n"/>
+      <c r="I84" s="38" t="n"/>
+      <c r="J84" s="38" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-specialist-in-islamabad/</t>
+        </is>
+      </c>
+      <c r="B85" s="34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C85" s="34" t="n">
+        <v>3364</v>
+      </c>
+      <c r="D85" s="35" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="E85" s="36" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F85" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G85" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H85" s="38" t="n"/>
+      <c r="I85" s="38" t="n"/>
+      <c r="J85" s="38" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-chicken-increase-dht/</t>
+        </is>
+      </c>
+      <c r="B86" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="C86" s="34" t="n">
+        <v>3299</v>
+      </c>
+      <c r="D86" s="35" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="E86" s="36" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="F86" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G86" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into a single DHT/diet FAQ section</t>
+        </is>
+      </c>
+      <c r="H86" s="38" t="n"/>
+      <c r="I86" s="38" t="n"/>
+      <c r="J86" s="38" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-fibers/</t>
+        </is>
+      </c>
+      <c r="B87" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C87" s="34" t="n">
+        <v>3262</v>
+      </c>
+      <c r="D87" s="35" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="E87" s="36" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="F87" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G87" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H87" s="38" t="n"/>
+      <c r="I87" s="38" t="n"/>
+      <c r="J87" s="38" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/low-blood-pressure-and-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B88" s="34" t="n">
+        <v>79</v>
+      </c>
+      <c r="C88" s="34" t="n">
+        <v>3176</v>
+      </c>
+      <c r="D88" s="35" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="E88" s="36" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="F88" s="33" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G88" s="37" t="inlineStr">
+        <is>
+          <t>Merge/301</t>
+        </is>
+      </c>
+      <c r="H88" s="38" t="n"/>
+      <c r="I88" s="38" t="n"/>
+      <c r="J88" s="38" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/blood-pressure-medications/</t>
+        </is>
+      </c>
+      <c r="B89" s="34" t="n">
+        <v>29</v>
+      </c>
+      <c r="C89" s="34" t="n">
+        <v>3159</v>
+      </c>
+      <c r="D89" s="35" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="E89" s="36" t="n">
+        <v>22.51</v>
+      </c>
+      <c r="F89" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G89" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H89" s="38" t="n"/>
+      <c r="I89" s="38" t="n"/>
+      <c r="J89" s="38" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/how-much-hair-do-humans-have/</t>
+        </is>
+      </c>
+      <c r="B90" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C90" s="34" t="n">
+        <v>3080</v>
+      </c>
+      <c r="D90" s="35" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="E90" s="36" t="n">
+        <v>38.35</v>
+      </c>
+      <c r="F90" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G90" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H90" s="38" t="n"/>
+      <c r="I90" s="38" t="n"/>
+      <c r="J90" s="38" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/finasteride-and-muscle-growth/</t>
+        </is>
+      </c>
+      <c r="B91" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C91" s="34" t="n">
+        <v>3043</v>
+      </c>
+      <c r="D91" s="35" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="E91" s="36" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="F91" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G91" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H91" s="38" t="n"/>
+      <c r="I91" s="38" t="n"/>
+      <c r="J91" s="38" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/scalp-reduction-surgery/</t>
+        </is>
+      </c>
+      <c r="B92" s="34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C92" s="34" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D92" s="35" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="E92" s="36" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="F92" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G92" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H92" s="38" t="n"/>
+      <c r="I92" s="38" t="n"/>
+      <c r="J92" s="38" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/finasteride-mtf/</t>
+        </is>
+      </c>
+      <c r="B93" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="C93" s="34" t="n">
+        <v>3003</v>
+      </c>
+      <c r="D93" s="35" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="E93" s="36" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="F93" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G93" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H93" s="38" t="n"/>
+      <c r="I93" s="38" t="n"/>
+      <c r="J93" s="38" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-valsartan-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B94" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="C94" s="34" t="n">
+        <v>2946</v>
+      </c>
+      <c r="D94" s="35" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="E94" s="36" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F94" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G94" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H94" s="38" t="n"/>
+      <c r="I94" s="38" t="n"/>
+      <c r="J94" s="38" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-betamethasone-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B95" s="34" t="n">
+        <v>31</v>
+      </c>
+      <c r="C95" s="34" t="n">
+        <v>2919</v>
+      </c>
+      <c r="D95" s="35" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="E95" s="36" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="F95" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G95" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H95" s="38" t="n"/>
+      <c r="I95" s="38" t="n"/>
+      <c r="J95" s="38" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-cost-in-pakistan/hair-transplant-cost-in-karachi/</t>
+        </is>
+      </c>
+      <c r="B96" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C96" s="34" t="n">
+        <v>2890</v>
+      </c>
+      <c r="D96" s="35" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="E96" s="36" t="n">
+        <v>44.53</v>
+      </c>
+      <c r="F96" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G96" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H96" s="38" t="n"/>
+      <c r="I96" s="38" t="n"/>
+      <c r="J96" s="38" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/allergic-to-fake-hair/</t>
+        </is>
+      </c>
+      <c r="B97" s="34" t="n">
+        <v>21</v>
+      </c>
+      <c r="C97" s="34" t="n">
+        <v>2866</v>
+      </c>
+      <c r="D97" s="35" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="E97" s="36" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="F97" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G97" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H97" s="38" t="n"/>
+      <c r="I97" s="38" t="n"/>
+      <c r="J97" s="38" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/how-to-lighten-hair-when-dyed-too-dark/</t>
+        </is>
+      </c>
+      <c r="B98" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C98" s="34" t="n">
+        <v>2865</v>
+      </c>
+      <c r="D98" s="35" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E98" s="36" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="F98" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G98" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H98" s="38" t="n"/>
+      <c r="I98" s="38" t="n"/>
+      <c r="J98" s="38" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/best-face-wash-to-prevent-ingrown-hairs/</t>
+        </is>
+      </c>
+      <c r="B99" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C99" s="34" t="n">
+        <v>2831</v>
+      </c>
+      <c r="D99" s="35" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="E99" s="36" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="F99" s="33" t="inlineStr">
+        <is>
+          <t>Facial/skincare (adjacent vertical)</t>
+        </is>
+      </c>
+      <c r="G99" s="37" t="inlineStr">
+        <is>
+          <t>Business decision: keep as its own section if the clinic offers these, else prune</t>
+        </is>
+      </c>
+      <c r="H99" s="38" t="n"/>
+      <c r="I99" s="38" t="n"/>
+      <c r="J99" s="38" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/benefits-of-monthly-hydrafacial/</t>
+        </is>
+      </c>
+      <c r="B100" s="34" t="n">
+        <v>24</v>
+      </c>
+      <c r="C100" s="34" t="n">
+        <v>2806</v>
+      </c>
+      <c r="D100" s="35" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="E100" s="36" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="F100" s="33" t="inlineStr">
+        <is>
+          <t>Facial/skincare (adjacent vertical)</t>
+        </is>
+      </c>
+      <c r="G100" s="37" t="inlineStr">
+        <is>
+          <t>Business decision: keep as its own section if the clinic offers these, else prune</t>
+        </is>
+      </c>
+      <c r="H100" s="38" t="n"/>
+      <c r="I100" s="38" t="n"/>
+      <c r="J100" s="38" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/scalp-exercises-expert-guide/</t>
+        </is>
+      </c>
+      <c r="B101" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="C101" s="34" t="n">
+        <v>2757</v>
+      </c>
+      <c r="D101" s="35" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="E101" s="36" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="F101" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G101" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H101" s="38" t="n"/>
+      <c r="I101" s="38" t="n"/>
+      <c r="J101" s="38" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-zyn-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B102" s="34" t="n">
+        <v>25</v>
+      </c>
+      <c r="C102" s="34" t="n">
+        <v>2744</v>
+      </c>
+      <c r="D102" s="35" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="E102" s="36" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="F102" s="33" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G102" s="37" t="inlineStr">
+        <is>
+          <t>Merge/301</t>
+        </is>
+      </c>
+      <c r="H102" s="38" t="n"/>
+      <c r="I102" s="38" t="n"/>
+      <c r="J102" s="38" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-alpha-lipoic-acid-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B103" s="34" t="n">
+        <v>44</v>
+      </c>
+      <c r="C103" s="34" t="n">
+        <v>2742</v>
+      </c>
+      <c r="D103" s="35" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="E103" s="36" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="F103" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G103" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H103" s="38" t="n"/>
+      <c r="I103" s="38" t="n"/>
+      <c r="J103" s="38" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-cost-in-pakistan/hair-transplant-cost-in-islamabad/</t>
+        </is>
+      </c>
+      <c r="B104" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="C104" s="34" t="n">
+        <v>2709</v>
+      </c>
+      <c r="D104" s="35" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="E104" s="36" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="F104" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G104" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H104" s="38" t="n"/>
+      <c r="I104" s="38" t="n"/>
+      <c r="J104" s="38" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/top-dht-blocker-foods/</t>
+        </is>
+      </c>
+      <c r="B105" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="C105" s="34" t="n">
+        <v>2698</v>
+      </c>
+      <c r="D105" s="35" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="E105" s="36" t="n">
+        <v>38.35</v>
+      </c>
+      <c r="F105" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G105" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H105" s="38" t="n"/>
+      <c r="I105" s="38" t="n"/>
+      <c r="J105" s="38" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/progesterone-female-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B106" s="34" t="n">
+        <v>15</v>
+      </c>
+      <c r="C106" s="34" t="n">
+        <v>2635</v>
+      </c>
+      <c r="D106" s="35" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="E106" s="36" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="F106" s="33" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G106" s="37" t="inlineStr">
+        <is>
+          <t>Merge/301</t>
+        </is>
+      </c>
+      <c r="H106" s="38" t="n"/>
+      <c r="I106" s="38" t="n"/>
+      <c r="J106" s="38" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-you-take-finasteride-3-times-a-week/</t>
+        </is>
+      </c>
+      <c r="B107" s="34" t="n">
+        <v>49</v>
+      </c>
+      <c r="C107" s="34" t="n">
+        <v>2617</v>
+      </c>
+      <c r="D107" s="35" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="E107" s="36" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="F107" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G107" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H107" s="38" t="n"/>
+      <c r="I107" s="38" t="n"/>
+      <c r="J107" s="38" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/finasteride-0-01-topical/</t>
+        </is>
+      </c>
+      <c r="B108" s="34" t="n">
+        <v>63</v>
+      </c>
+      <c r="C108" s="34" t="n">
+        <v>2593</v>
+      </c>
+      <c r="D108" s="35" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="E108" s="36" t="n">
+        <v>33.93</v>
+      </c>
+      <c r="F108" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G108" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H108" s="38" t="n"/>
+      <c r="I108" s="38" t="n"/>
+      <c r="J108" s="38" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-coconut-oil-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B109" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C109" s="34" t="n">
+        <v>2517</v>
+      </c>
+      <c r="D109" s="35" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="E109" s="36" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="F109" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G109" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H109" s="38" t="n"/>
+      <c r="I109" s="38" t="n"/>
+      <c r="J109" s="38" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-cost-in-pakistan/hair-transplant-cost-in-faisalabad/</t>
+        </is>
+      </c>
+      <c r="B110" s="34" t="n">
+        <v>19</v>
+      </c>
+      <c r="C110" s="34" t="n">
+        <v>2447</v>
+      </c>
+      <c r="D110" s="35" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="E110" s="36" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="F110" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G110" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H110" s="38" t="n"/>
+      <c r="I110" s="38" t="n"/>
+      <c r="J110" s="38" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-hep-c-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B111" s="34" t="n">
+        <v>17</v>
+      </c>
+      <c r="C111" s="34" t="n">
+        <v>2331</v>
+      </c>
+      <c r="D111" s="35" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="E111" s="36" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="F111" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G111" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H111" s="38" t="n"/>
+      <c r="I111" s="38" t="n"/>
+      <c r="J111" s="38" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/biotin-and-finasteride/</t>
+        </is>
+      </c>
+      <c r="B112" s="34" t="n">
+        <v>15</v>
+      </c>
+      <c r="C112" s="34" t="n">
+        <v>2297</v>
+      </c>
+      <c r="D112" s="35" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="E112" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="F112" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G112" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H112" s="38" t="n"/>
+      <c r="I112" s="38" t="n"/>
+      <c r="J112" s="38" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/advancehair-transplant-center/</t>
+        </is>
+      </c>
+      <c r="B113" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="C113" s="34" t="n">
+        <v>2270</v>
+      </c>
+      <c r="D113" s="35" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="E113" s="36" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F113" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G113" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H113" s="38" t="n"/>
+      <c r="I113" s="38" t="n"/>
+      <c r="J113" s="38" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-diltiazem-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B114" s="34" t="n">
+        <v>26</v>
+      </c>
+      <c r="C114" s="34" t="n">
+        <v>2258</v>
+      </c>
+      <c r="D114" s="35" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="E114" s="36" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="F114" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G114" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H114" s="38" t="n"/>
+      <c r="I114" s="38" t="n"/>
+      <c r="J114" s="38" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-finasteride-cause-brain-fog/</t>
+        </is>
+      </c>
+      <c r="B115" s="34" t="n">
+        <v>26</v>
+      </c>
+      <c r="C115" s="34" t="n">
+        <v>2228</v>
+      </c>
+      <c r="D115" s="35" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="E115" s="36" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="F115" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G115" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H115" s="38" t="n"/>
+      <c r="I115" s="38" t="n"/>
+      <c r="J115" s="38" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/cortisone-shots-for-hair-growth-before-and-after/</t>
+        </is>
+      </c>
+      <c r="B116" s="34" t="n">
+        <v>27</v>
+      </c>
+      <c r="C116" s="34" t="n">
+        <v>2225</v>
+      </c>
+      <c r="D116" s="35" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="E116" s="36" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="F116" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G116" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H116" s="38" t="n"/>
+      <c r="I116" s="38" t="n"/>
+      <c r="J116" s="38" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/best-hair-products-for-teens/</t>
+        </is>
+      </c>
+      <c r="B117" s="34" t="n">
+        <v>25</v>
+      </c>
+      <c r="C117" s="34" t="n">
+        <v>2216</v>
+      </c>
+      <c r="D117" s="35" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="E117" s="36" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="F117" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G117" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H117" s="38" t="n"/>
+      <c r="I117" s="38" t="n"/>
+      <c r="J117" s="38" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/white-piedra/</t>
+        </is>
+      </c>
+      <c r="B118" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C118" s="34" t="n">
+        <v>2175</v>
+      </c>
+      <c r="D118" s="35" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="E118" s="36" t="n">
+        <v>36.19</v>
+      </c>
+      <c r="F118" s="33" t="inlineStr">
+        <is>
+          <t>Dermatology/symptom content (tangential)</t>
+        </is>
+      </c>
+      <c r="G118" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate - low priority</t>
+        </is>
+      </c>
+      <c r="H118" s="38" t="n"/>
+      <c r="I118" s="38" t="n"/>
+      <c r="J118" s="38" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/aspirin-and-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B119" s="34" t="n">
+        <v>14</v>
+      </c>
+      <c r="C119" s="34" t="n">
+        <v>2164</v>
+      </c>
+      <c r="D119" s="35" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="E119" s="36" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="F119" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G119" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H119" s="38" t="n"/>
+      <c r="I119" s="38" t="n"/>
+      <c r="J119" s="38" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/is-hair-class-or-individual-evidence/</t>
+        </is>
+      </c>
+      <c r="B120" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C120" s="34" t="n">
+        <v>2135</v>
+      </c>
+      <c r="D120" s="35" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="E120" s="36" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F120" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G120" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H120" s="38" t="n"/>
+      <c r="I120" s="38" t="n"/>
+      <c r="J120" s="38" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-you-stop-taking-finasteride-suddenly/</t>
+        </is>
+      </c>
+      <c r="B121" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C121" s="34" t="n">
+        <v>2117</v>
+      </c>
+      <c r="D121" s="35" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="E121" s="36" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="F121" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G121" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H121" s="38" t="n"/>
+      <c r="I121" s="38" t="n"/>
+      <c r="J121" s="38" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-sibo-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B122" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="C122" s="34" t="n">
+        <v>2106</v>
+      </c>
+      <c r="D122" s="35" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="E122" s="36" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="F122" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G122" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H122" s="38" t="n"/>
+      <c r="I122" s="38" t="n"/>
+      <c r="J122" s="38" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/oral-and-topical-finasteride-together/</t>
+        </is>
+      </c>
+      <c r="B123" s="34" t="n">
+        <v>34</v>
+      </c>
+      <c r="C123" s="34" t="n">
+        <v>2105</v>
+      </c>
+      <c r="D123" s="35" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="E123" s="36" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="F123" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G123" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H123" s="38" t="n"/>
+      <c r="I123" s="38" t="n"/>
+      <c r="J123" s="38" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/pimples-on-the-donor-area-after-hair-transplant/</t>
+        </is>
+      </c>
+      <c r="B124" s="34" t="n">
+        <v>16</v>
+      </c>
+      <c r="C124" s="34" t="n">
+        <v>2033</v>
+      </c>
+      <c r="D124" s="35" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="E124" s="36" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="F124" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G124" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H124" s="38" t="n"/>
+      <c r="I124" s="38" t="n"/>
+      <c r="J124" s="38" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/icon-hair-replacement-in-pakistan/</t>
+        </is>
+      </c>
+      <c r="B125" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C125" s="34" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D125" s="35" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="E125" s="36" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="F125" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G125" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H125" s="38" t="n"/>
+      <c r="I125" s="38" t="n"/>
+      <c r="J125" s="38" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/pakistani-celebrities-with-hair-transplant/</t>
+        </is>
+      </c>
+      <c r="B126" s="34" t="n">
+        <v>53</v>
+      </c>
+      <c r="C126" s="34" t="n">
+        <v>1916</v>
+      </c>
+      <c r="D126" s="35" t="n">
+        <v>0.0277</v>
+      </c>
+      <c r="E126" s="36" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="F126" s="33" t="inlineStr">
+        <is>
+          <t>Celebrity/pop-culture</t>
+        </is>
+      </c>
+      <c r="G126" s="37" t="inlineStr">
+        <is>
+          <t>Keep (local social proof)</t>
+        </is>
+      </c>
+      <c r="H126" s="38" t="n"/>
+      <c r="I126" s="38" t="n"/>
+      <c r="J126" s="38" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/best-products-for-hair-growth-after-chemo/</t>
+        </is>
+      </c>
+      <c r="B127" s="34" t="n">
+        <v>39</v>
+      </c>
+      <c r="C127" s="34" t="n">
+        <v>1863</v>
+      </c>
+      <c r="D127" s="35" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="E127" s="36" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="F127" s="33" t="inlineStr">
+        <is>
+          <t>Cancer/chemo hair loss</t>
+        </is>
+      </c>
+      <c r="G127" s="37" t="inlineStr">
+        <is>
+          <t>Low-priority keep (adjacent audience, not core)</t>
+        </is>
+      </c>
+      <c r="H127" s="38" t="n"/>
+      <c r="I127" s="38" t="n"/>
+      <c r="J127" s="38" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-dermatologist-in-islamabad/</t>
+        </is>
+      </c>
+      <c r="B128" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="C128" s="34" t="n">
+        <v>1851</v>
+      </c>
+      <c r="D128" s="35" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="E128" s="36" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="F128" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G128" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H128" s="38" t="n"/>
+      <c r="I128" s="38" t="n"/>
+      <c r="J128" s="38" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/best-treatments-for-alopecia-areata-in-islamabad/</t>
+        </is>
+      </c>
+      <c r="B129" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="C129" s="34" t="n">
+        <v>1835</v>
+      </c>
+      <c r="D129" s="35" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="E129" s="36" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="F129" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G129" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H129" s="38" t="n"/>
+      <c r="I129" s="38" t="n"/>
+      <c r="J129" s="38" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/switching-from-oral-to-topical-finasteride/</t>
+        </is>
+      </c>
+      <c r="B130" s="34" t="n">
+        <v>29</v>
+      </c>
+      <c r="C130" s="34" t="n">
+        <v>1772</v>
+      </c>
+      <c r="D130" s="35" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="E130" s="36" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="F130" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G130" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H130" s="38" t="n"/>
+      <c r="I130" s="38" t="n"/>
+      <c r="J130" s="38" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-colchicine-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B131" s="34" t="n">
+        <v>36</v>
+      </c>
+      <c r="C131" s="34" t="n">
+        <v>1770</v>
+      </c>
+      <c r="D131" s="35" t="n">
+        <v>0.0203</v>
+      </c>
+      <c r="E131" s="36" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="F131" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G131" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H131" s="38" t="n"/>
+      <c r="I131" s="38" t="n"/>
+      <c r="J131" s="38" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/best-shampoo-to-use-after-hair-transplant/</t>
+        </is>
+      </c>
+      <c r="B132" s="34" t="n">
+        <v>36</v>
+      </c>
+      <c r="C132" s="34" t="n">
+        <v>1769</v>
+      </c>
+      <c r="D132" s="35" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="E132" s="36" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="F132" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G132" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H132" s="38" t="n"/>
+      <c r="I132" s="38" t="n"/>
+      <c r="J132" s="38" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/positive-therapeutic-effects-of-finasteride/</t>
+        </is>
+      </c>
+      <c r="B133" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C133" s="34" t="n">
+        <v>1758</v>
+      </c>
+      <c r="D133" s="35" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="E133" s="36" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="F133" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G133" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H133" s="38" t="n"/>
+      <c r="I133" s="38" t="n"/>
+      <c r="J133" s="38" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/about/</t>
+        </is>
+      </c>
+      <c r="B134" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="C134" s="34" t="n">
+        <v>1684</v>
+      </c>
+      <c r="D134" s="35" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="E134" s="36" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="F134" s="33" t="inlineStr">
+        <is>
+          <t>Core site page</t>
+        </is>
+      </c>
+      <c r="G134" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H134" s="38" t="n"/>
+      <c r="I134" s="38" t="n"/>
+      <c r="J134" s="38" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-nizoral-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B135" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C135" s="34" t="n">
+        <v>1652</v>
+      </c>
+      <c r="D135" s="35" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="E135" s="36" t="n">
+        <v>49.68</v>
+      </c>
+      <c r="F135" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G135" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H135" s="38" t="n"/>
+      <c r="I135" s="38" t="n"/>
+      <c r="J135" s="38" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/when-to-stop-finasteride-before-pregnancy/</t>
+        </is>
+      </c>
+      <c r="B136" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="C136" s="34" t="n">
+        <v>1637</v>
+      </c>
+      <c r="D136" s="35" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="E136" s="36" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="F136" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G136" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H136" s="38" t="n"/>
+      <c r="I136" s="38" t="n"/>
+      <c r="J136" s="38" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/title-can-progesterone-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B137" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C137" s="34" t="n">
+        <v>1616</v>
+      </c>
+      <c r="D137" s="35" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="E137" s="36" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="F137" s="33" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G137" s="37" t="inlineStr">
+        <is>
+          <t>Merge/301</t>
+        </is>
+      </c>
+      <c r="H137" s="38" t="n"/>
+      <c r="I137" s="38" t="n"/>
+      <c r="J137" s="38" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-finasteride-cause-dry-eyes/</t>
+        </is>
+      </c>
+      <c r="B138" s="34" t="n">
+        <v>27</v>
+      </c>
+      <c r="C138" s="34" t="n">
+        <v>1612</v>
+      </c>
+      <c r="D138" s="35" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="E138" s="36" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="F138" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G138" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H138" s="38" t="n"/>
+      <c r="I138" s="38" t="n"/>
+      <c r="J138" s="38" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/benefits-of-cholesterol-hair-treatment/</t>
+        </is>
+      </c>
+      <c r="B139" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C139" s="34" t="n">
+        <v>1603</v>
+      </c>
+      <c r="D139" s="35" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="E139" s="36" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="F139" s="33" t="inlineStr">
+        <is>
+          <t>Facial/skincare (adjacent vertical)</t>
+        </is>
+      </c>
+      <c r="G139" s="37" t="inlineStr">
+        <is>
+          <t>Business decision: keep as its own section if the clinic offers these, else prune</t>
+        </is>
+      </c>
+      <c r="H139" s="38" t="n"/>
+      <c r="I139" s="38" t="n"/>
+      <c r="J139" s="38" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/which-doctor-is-best-for-hair-problems/</t>
+        </is>
+      </c>
+      <c r="B140" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C140" s="34" t="n">
+        <v>1599</v>
+      </c>
+      <c r="D140" s="35" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="E140" s="36" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="F140" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G140" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H140" s="38" t="n"/>
+      <c r="I140" s="38" t="n"/>
+      <c r="J140" s="38" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/colon-cancer-and-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B141" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C141" s="34" t="n">
+        <v>1577</v>
+      </c>
+      <c r="D141" s="35" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="E141" s="36" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="F141" s="33" t="inlineStr">
+        <is>
+          <t>Cancer/chemo hair loss</t>
+        </is>
+      </c>
+      <c r="G141" s="37" t="inlineStr">
+        <is>
+          <t>Low-priority keep (adjacent audience, not core)</t>
+        </is>
+      </c>
+      <c r="H141" s="38" t="n"/>
+      <c r="I141" s="38" t="n"/>
+      <c r="J141" s="38" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-sleeping-on-one-side-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B142" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C142" s="34" t="n">
+        <v>1557</v>
+      </c>
+      <c r="D142" s="35" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="E142" s="36" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="F142" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G142" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H142" s="38" t="n"/>
+      <c r="I142" s="38" t="n"/>
+      <c r="J142" s="38" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/whats-the-best-way-to-treat-bald-spots-in-4c-hair/</t>
+        </is>
+      </c>
+      <c r="B143" s="34" t="n">
+        <v>16</v>
+      </c>
+      <c r="C143" s="34" t="n">
+        <v>1541</v>
+      </c>
+      <c r="D143" s="35" t="n">
+        <v>0.0104</v>
+      </c>
+      <c r="E143" s="36" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="F143" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G143" s="37" t="inlineStr">
+        <is>
+          <t>Keep, but merge into the alopecia areata page</t>
+        </is>
+      </c>
+      <c r="H143" s="38" t="n"/>
+      <c r="I143" s="38" t="n"/>
+      <c r="J143" s="38" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-chlamydia-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B144" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="C144" s="34" t="n">
+        <v>1515</v>
+      </c>
+      <c r="D144" s="35" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="E144" s="36" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="F144" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G144" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H144" s="38" t="n"/>
+      <c r="I144" s="38" t="n"/>
+      <c r="J144" s="38" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-zig-zag-hairline/</t>
+        </is>
+      </c>
+      <c r="B145" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C145" s="34" t="n">
+        <v>1509</v>
+      </c>
+      <c r="D145" s="35" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="E145" s="36" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="F145" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G145" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H145" s="38" t="n"/>
+      <c r="I145" s="38" t="n"/>
+      <c r="J145" s="38" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-cost-in-pakistan/hair-transplant-cost-in-multan/</t>
+        </is>
+      </c>
+      <c r="B146" s="34" t="n">
+        <v>28</v>
+      </c>
+      <c r="C146" s="34" t="n">
+        <v>1485</v>
+      </c>
+      <c r="D146" s="35" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="E146" s="36" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="F146" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G146" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H146" s="38" t="n"/>
+      <c r="I146" s="38" t="n"/>
+      <c r="J146" s="38" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/headphones-and-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B147" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="C147" s="34" t="n">
+        <v>1445</v>
+      </c>
+      <c r="D147" s="35" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="E147" s="36" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="F147" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G147" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H147" s="38" t="n"/>
+      <c r="I147" s="38" t="n"/>
+      <c r="J147" s="38" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/prp-hair-treatment-in-islamabad/</t>
+        </is>
+      </c>
+      <c r="B148" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C148" s="34" t="n">
+        <v>1424</v>
+      </c>
+      <c r="D148" s="35" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="E148" s="36" t="n">
+        <v>30.29</v>
+      </c>
+      <c r="F148" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G148" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H148" s="38" t="n"/>
+      <c r="I148" s="38" t="n"/>
+      <c r="J148" s="38" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/allergic-to-hair-extensions/</t>
+        </is>
+      </c>
+      <c r="B149" s="34" t="n">
+        <v>22</v>
+      </c>
+      <c r="C149" s="34" t="n">
+        <v>1412</v>
+      </c>
+      <c r="D149" s="35" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="E149" s="36" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="F149" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G149" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H149" s="38" t="n"/>
+      <c r="I149" s="38" t="n"/>
+      <c r="J149" s="38" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-fenugreek-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B150" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C150" s="34" t="n">
+        <v>1361</v>
+      </c>
+      <c r="D150" s="35" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="E150" s="36" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F150" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G150" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H150" s="38" t="n"/>
+      <c r="I150" s="38" t="n"/>
+      <c r="J150" s="38" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/how-many-grafts-are-in-a-full-head/</t>
+        </is>
+      </c>
+      <c r="B151" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C151" s="34" t="n">
+        <v>1347</v>
+      </c>
+      <c r="D151" s="35" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="E151" s="36" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="F151" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G151" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H151" s="38" t="n"/>
+      <c r="I151" s="38" t="n"/>
+      <c r="J151" s="38" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-fluoxetine-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B152" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C152" s="34" t="n">
+        <v>1343</v>
+      </c>
+      <c r="D152" s="35" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="E152" s="36" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="F152" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G152" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H152" s="38" t="n"/>
+      <c r="I152" s="38" t="n"/>
+      <c r="J152" s="38" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-loss-treatment-in-pakistan/</t>
+        </is>
+      </c>
+      <c r="B153" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C153" s="34" t="n">
+        <v>1331</v>
+      </c>
+      <c r="D153" s="35" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="E153" s="36" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="F153" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G153" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H153" s="38" t="n"/>
+      <c r="I153" s="38" t="n"/>
+      <c r="J153" s="38" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/beard-hair-gel-benefits-best-picks/</t>
+        </is>
+      </c>
+      <c r="B154" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C154" s="34" t="n">
+        <v>1295</v>
+      </c>
+      <c r="D154" s="35" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="E154" s="36" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="F154" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G154" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H154" s="38" t="n"/>
+      <c r="I154" s="38" t="n"/>
+      <c r="J154" s="38" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-bcaa-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B155" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C155" s="34" t="n">
+        <v>1277</v>
+      </c>
+      <c r="D155" s="35" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="E155" s="36" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="F155" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G155" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H155" s="38" t="n"/>
+      <c r="I155" s="38" t="n"/>
+      <c r="J155" s="38" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/how-to-apply-topical-finasteride/</t>
+        </is>
+      </c>
+      <c r="B156" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="C156" s="34" t="n">
+        <v>1262</v>
+      </c>
+      <c r="D156" s="35" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="E156" s="36" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F156" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G156" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H156" s="38" t="n"/>
+      <c r="I156" s="38" t="n"/>
+      <c r="J156" s="38" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-cost-in-pakistan/hair-transplant-cost-in-rawalpindi/</t>
+        </is>
+      </c>
+      <c r="B157" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="C157" s="34" t="n">
+        <v>1167</v>
+      </c>
+      <c r="D157" s="35" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="E157" s="36" t="n">
+        <v>38.43</v>
+      </c>
+      <c r="F157" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G157" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H157" s="38" t="n"/>
+      <c r="I157" s="38" t="n"/>
+      <c r="J157" s="38" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/why-does-my-scalp-itch-after-exercise/</t>
+        </is>
+      </c>
+      <c r="B158" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C158" s="34" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D158" s="35" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="E158" s="36" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="F158" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G158" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H158" s="38" t="n"/>
+      <c r="I158" s="38" t="n"/>
+      <c r="J158" s="38" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/will-amlodipine-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B159" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C159" s="34" t="n">
+        <v>1138</v>
+      </c>
+      <c r="D159" s="35" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="E159" s="36" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="F159" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G159" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H159" s="38" t="n"/>
+      <c r="I159" s="38" t="n"/>
+      <c r="J159" s="38" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/finasteride-psa-calculator/</t>
+        </is>
+      </c>
+      <c r="B160" s="34" t="n">
+        <v>44</v>
+      </c>
+      <c r="C160" s="34" t="n">
+        <v>1129</v>
+      </c>
+      <c r="D160" s="35" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="E160" s="36" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="F160" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G160" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H160" s="38" t="n"/>
+      <c r="I160" s="38" t="n"/>
+      <c r="J160" s="38" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/eyebrow-transplant/eyebrow-transplant-regret-common-mistakes-to-avoid/</t>
+        </is>
+      </c>
+      <c r="B161" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C161" s="34" t="n">
+        <v>1129</v>
+      </c>
+      <c r="D161" s="35" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="E161" s="36" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="F161" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G161" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H161" s="38" t="n"/>
+      <c r="I161" s="38" t="n"/>
+      <c r="J161" s="38" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-low-blood-pressure-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B162" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C162" s="34" t="n">
+        <v>1091</v>
+      </c>
+      <c r="D162" s="35" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="E162" s="36" t="n">
+        <v>22.76</v>
+      </c>
+      <c r="F162" s="33" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G162" s="37" t="inlineStr">
+        <is>
+          <t>Merge/301</t>
+        </is>
+      </c>
+      <c r="H162" s="38" t="n"/>
+      <c r="I162" s="38" t="n"/>
+      <c r="J162" s="38" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/war-trauma-turns-childrens-hair-grey/</t>
+        </is>
+      </c>
+      <c r="B163" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C163" s="34" t="n">
+        <v>1086</v>
+      </c>
+      <c r="D163" s="35" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="E163" s="36" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F163" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G163" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H163" s="38" t="n"/>
+      <c r="I163" s="38" t="n"/>
+      <c r="J163" s="38" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-in-pakistan-ultimate-guide/understanding-the-hair-loss-epidemic-in-pakistan/</t>
+        </is>
+      </c>
+      <c r="B164" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C164" s="34" t="n">
+        <v>1069</v>
+      </c>
+      <c r="D164" s="35" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="E164" s="36" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="F164" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G164" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H164" s="38" t="n"/>
+      <c r="I164" s="38" t="n"/>
+      <c r="J164" s="38" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/contact/</t>
+        </is>
+      </c>
+      <c r="B165" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="C165" s="34" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D165" s="35" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="E165" s="36" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="F165" s="33" t="inlineStr">
+        <is>
+          <t>Core site page</t>
+        </is>
+      </c>
+      <c r="G165" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H165" s="38" t="n"/>
+      <c r="I165" s="38" t="n"/>
+      <c r="J165" s="38" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-atorvastatin-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B166" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C166" s="34" t="n">
+        <v>1063</v>
+      </c>
+      <c r="D166" s="35" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="E166" s="36" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="F166" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G166" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H166" s="38" t="n"/>
+      <c r="I166" s="38" t="n"/>
+      <c r="J166" s="38" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-cyclosporine-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B167" s="34" t="n">
+        <v>15</v>
+      </c>
+      <c r="C167" s="34" t="n">
+        <v>1062</v>
+      </c>
+      <c r="D167" s="35" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="E167" s="36" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="F167" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G167" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H167" s="38" t="n"/>
+      <c r="I167" s="38" t="n"/>
+      <c r="J167" s="38" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/how-to-reduce-5-alpha-reductase-naturally/</t>
+        </is>
+      </c>
+      <c r="B168" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C168" s="34" t="n">
+        <v>1036</v>
+      </c>
+      <c r="D168" s="35" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="E168" s="36" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="F168" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G168" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into DHT/finasteride FAQ hub</t>
+        </is>
+      </c>
+      <c r="H168" s="38" t="n"/>
+      <c r="I168" s="38" t="n"/>
+      <c r="J168" s="38" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-cost-in-pakistan/hair-transplant-cost-in-gujranwala/</t>
+        </is>
+      </c>
+      <c r="B169" s="34" t="n">
+        <v>17</v>
+      </c>
+      <c r="C169" s="34" t="n">
+        <v>1029</v>
+      </c>
+      <c r="D169" s="35" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="E169" s="36" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="F169" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G169" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H169" s="38" t="n"/>
+      <c r="I169" s="38" t="n"/>
+      <c r="J169" s="38" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-heart-problems-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B170" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C170" s="34" t="n">
+        <v>991</v>
+      </c>
+      <c r="D170" s="35" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="E170" s="36" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="F170" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G170" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H170" s="38" t="n"/>
+      <c r="I170" s="38" t="n"/>
+      <c r="J170" s="38" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-donor-area-complete-guide/burning-sensation-in-donor-area-after-hair-transplant/</t>
+        </is>
+      </c>
+      <c r="B171" s="34" t="n">
+        <v>15</v>
+      </c>
+      <c r="C171" s="34" t="n">
+        <v>978</v>
+      </c>
+      <c r="D171" s="35" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="E171" s="36" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="F171" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G171" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H171" s="38" t="n"/>
+      <c r="I171" s="38" t="n"/>
+      <c r="J171" s="38" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-muslims-do-hair-transplants/</t>
+        </is>
+      </c>
+      <c r="B172" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C172" s="34" t="n">
+        <v>972</v>
+      </c>
+      <c r="D172" s="35" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="E172" s="36" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="F172" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G172" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H172" s="38" t="n"/>
+      <c r="I172" s="38" t="n"/>
+      <c r="J172" s="38" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-cost-in-pakistan/hair-transplant-cost-in-peshawar/</t>
+        </is>
+      </c>
+      <c r="B173" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="C173" s="34" t="n">
+        <v>948</v>
+      </c>
+      <c r="D173" s="35" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="E173" s="36" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F173" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G173" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H173" s="38" t="n"/>
+      <c r="I173" s="38" t="n"/>
+      <c r="J173" s="38" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-you-make-your-own-topical-finasteride/</t>
+        </is>
+      </c>
+      <c r="B174" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="C174" s="34" t="n">
+        <v>900</v>
+      </c>
+      <c r="D174" s="35" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="E174" s="36" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="F174" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G174" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H174" s="38" t="n"/>
+      <c r="I174" s="38" t="n"/>
+      <c r="J174" s="38" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/eyebrow-transplant/</t>
+        </is>
+      </c>
+      <c r="B175" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C175" s="34" t="n">
+        <v>899</v>
+      </c>
+      <c r="D175" s="35" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="E175" s="36" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="F175" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G175" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H175" s="38" t="n"/>
+      <c r="I175" s="38" t="n"/>
+      <c r="J175" s="38" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/after-hair-transplant-can-i-wear-cap/</t>
+        </is>
+      </c>
+      <c r="B176" s="34" t="n">
+        <v>16</v>
+      </c>
+      <c r="C176" s="34" t="n">
+        <v>891</v>
+      </c>
+      <c r="D176" s="35" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E176" s="36" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="F176" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G176" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H176" s="38" t="n"/>
+      <c r="I176" s="38" t="n"/>
+      <c r="J176" s="38" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/how-much-does-5000-hair-grafts-cost-in-pakistan/</t>
+        </is>
+      </c>
+      <c r="B177" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C177" s="34" t="n">
+        <v>891</v>
+      </c>
+      <c r="D177" s="35" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="E177" s="36" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="F177" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G177" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H177" s="38" t="n"/>
+      <c r="I177" s="38" t="n"/>
+      <c r="J177" s="38" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/is-exosome-therapy-fda-approved/</t>
+        </is>
+      </c>
+      <c r="B178" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C178" s="34" t="n">
+        <v>875</v>
+      </c>
+      <c r="D178" s="35" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="E178" s="36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F178" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G178" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H178" s="38" t="n"/>
+      <c r="I178" s="38" t="n"/>
+      <c r="J178" s="38" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/celebrities-with-hairline-lowering-surgery/</t>
+        </is>
+      </c>
+      <c r="B179" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C179" s="34" t="n">
+        <v>867</v>
+      </c>
+      <c r="D179" s="35" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="E179" s="36" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="F179" s="33" t="inlineStr">
+        <is>
+          <t>Celebrity/pop-culture</t>
+        </is>
+      </c>
+      <c r="G179" s="37" t="inlineStr">
+        <is>
+          <t>Keep (local social proof)</t>
+        </is>
+      </c>
+      <c r="H179" s="38" t="n"/>
+      <c r="I179" s="38" t="n"/>
+      <c r="J179" s="38" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-food-allergies-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B180" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C180" s="34" t="n">
+        <v>867</v>
+      </c>
+      <c r="D180" s="35" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="E180" s="36" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="F180" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G180" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H180" s="38" t="n"/>
+      <c r="I180" s="38" t="n"/>
+      <c r="J180" s="38" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-cost-in-islamabad/</t>
+        </is>
+      </c>
+      <c r="B181" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C181" s="34" t="n">
+        <v>865</v>
+      </c>
+      <c r="D181" s="35" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="E181" s="36" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="F181" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G181" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H181" s="38" t="n"/>
+      <c r="I181" s="38" t="n"/>
+      <c r="J181" s="38" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/what-to-apply-to-the-donor-area-after-a-hair-transplant/</t>
+        </is>
+      </c>
+      <c r="B182" s="34" t="n">
+        <v>14</v>
+      </c>
+      <c r="C182" s="34" t="n">
+        <v>825</v>
+      </c>
+      <c r="D182" s="35" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="E182" s="36" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="F182" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G182" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H182" s="38" t="n"/>
+      <c r="I182" s="38" t="n"/>
+      <c r="J182" s="38" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/switching-from-finasteride-to-dutasteride/</t>
+        </is>
+      </c>
+      <c r="B183" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C183" s="34" t="n">
+        <v>801</v>
+      </c>
+      <c r="D183" s="35" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="E183" s="36" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="F183" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G183" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H183" s="38" t="n"/>
+      <c r="I183" s="38" t="n"/>
+      <c r="J183" s="38" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/musk-hair-color/</t>
+        </is>
+      </c>
+      <c r="B184" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C184" s="34" t="n">
+        <v>800</v>
+      </c>
+      <c r="D184" s="35" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="E184" s="36" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="F184" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G184" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H184" s="38" t="n"/>
+      <c r="I184" s="38" t="n"/>
+      <c r="J184" s="38" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-dialysis-make-you-lose-your-hair/</t>
+        </is>
+      </c>
+      <c r="B185" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C185" s="34" t="n">
+        <v>789</v>
+      </c>
+      <c r="D185" s="35" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="E185" s="36" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="F185" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G185" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H185" s="38" t="n"/>
+      <c r="I185" s="38" t="n"/>
+      <c r="J185" s="38" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-low-cortisol-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B186" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C186" s="34" t="n">
+        <v>784</v>
+      </c>
+      <c r="D186" s="35" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="E186" s="36" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="F186" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G186" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H186" s="38" t="n"/>
+      <c r="I186" s="38" t="n"/>
+      <c r="J186" s="38" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/what-is-trichophytic-closure/</t>
+        </is>
+      </c>
+      <c r="B187" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C187" s="34" t="n">
+        <v>778</v>
+      </c>
+      <c r="D187" s="35" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="E187" s="36" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="F187" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G187" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H187" s="38" t="n"/>
+      <c r="I187" s="38" t="n"/>
+      <c r="J187" s="38" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-before-and-after-what-to-expect/</t>
+        </is>
+      </c>
+      <c r="B188" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C188" s="34" t="n">
+        <v>762</v>
+      </c>
+      <c r="D188" s="35" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="E188" s="36" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="F188" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G188" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H188" s="38" t="n"/>
+      <c r="I188" s="38" t="n"/>
+      <c r="J188" s="38" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/botched-hair-transplant-infections/</t>
+        </is>
+      </c>
+      <c r="B189" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="C189" s="34" t="n">
+        <v>737</v>
+      </c>
+      <c r="D189" s="35" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="E189" s="36" t="n">
+        <v>66.38</v>
+      </c>
+      <c r="F189" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G189" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H189" s="38" t="n"/>
+      <c r="I189" s="38" t="n"/>
+      <c r="J189" s="38" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-damage-test/</t>
+        </is>
+      </c>
+      <c r="B190" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="C190" s="34" t="n">
+        <v>725</v>
+      </c>
+      <c r="D190" s="35" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="E190" s="36" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="F190" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G190" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H190" s="38" t="n"/>
+      <c r="I190" s="38" t="n"/>
+      <c r="J190" s="38" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-ivf-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B191" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C191" s="34" t="n">
+        <v>724</v>
+      </c>
+      <c r="D191" s="35" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="E191" s="36" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F191" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G191" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H191" s="38" t="n"/>
+      <c r="I191" s="38" t="n"/>
+      <c r="J191" s="38" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-loss-cure-for-men/</t>
+        </is>
+      </c>
+      <c r="B192" s="34" t="n">
+        <v>38</v>
+      </c>
+      <c r="C192" s="34" t="n">
+        <v>706</v>
+      </c>
+      <c r="D192" s="35" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="E192" s="36" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="F192" s="33" t="inlineStr">
+        <is>
+          <t>Generic informational (off-topic/zero-click)</t>
+        </is>
+      </c>
+      <c r="G192" s="37" t="inlineStr">
+        <is>
+          <t>Rework into the clinic's own protocol page rather than delete</t>
+        </is>
+      </c>
+      <c r="H192" s="38" t="n"/>
+      <c r="I192" s="38" t="n"/>
+      <c r="J192" s="38" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-vs-prp/</t>
+        </is>
+      </c>
+      <c r="B193" s="34" t="n">
+        <v>29</v>
+      </c>
+      <c r="C193" s="34" t="n">
+        <v>695</v>
+      </c>
+      <c r="D193" s="35" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="E193" s="36" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="F193" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G193" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H193" s="38" t="n"/>
+      <c r="I193" s="38" t="n"/>
+      <c r="J193" s="38" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-i-scratch-my-donor-area-after-hair-transplant/</t>
+        </is>
+      </c>
+      <c r="B194" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C194" s="34" t="n">
+        <v>694</v>
+      </c>
+      <c r="D194" s="35" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="E194" s="36" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="F194" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G194" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H194" s="38" t="n"/>
+      <c r="I194" s="38" t="n"/>
+      <c r="J194" s="38" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-glutathione-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B195" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C195" s="34" t="n">
+        <v>691</v>
+      </c>
+      <c r="D195" s="35" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="E195" s="36" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="F195" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G195" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H195" s="38" t="n"/>
+      <c r="I195" s="38" t="n"/>
+      <c r="J195" s="38" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/will-ai-cure-baldness/</t>
+        </is>
+      </c>
+      <c r="B196" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C196" s="34" t="n">
+        <v>653</v>
+      </c>
+      <c r="D196" s="35" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="E196" s="36" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="F196" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G196" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H196" s="38" t="n"/>
+      <c r="I196" s="38" t="n"/>
+      <c r="J196" s="38" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/body-hair-transplant-in-pakistan/</t>
+        </is>
+      </c>
+      <c r="B197" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="C197" s="34" t="n">
+        <v>641</v>
+      </c>
+      <c r="D197" s="35" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="E197" s="36" t="n">
+        <v>63.61</v>
+      </c>
+      <c r="F197" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G197" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H197" s="38" t="n"/>
+      <c r="I197" s="38" t="n"/>
+      <c r="J197" s="38" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-etoposide-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B198" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="C198" s="34" t="n">
+        <v>634</v>
+      </c>
+      <c r="D198" s="35" t="n">
+        <v>0.0284</v>
+      </c>
+      <c r="E198" s="36" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="F198" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G198" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H198" s="38" t="n"/>
+      <c r="I198" s="38" t="n"/>
+      <c r="J198" s="38" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-caboki-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B199" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C199" s="34" t="n">
+        <v>629</v>
+      </c>
+      <c r="D199" s="35" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="E199" s="36" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="F199" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G199" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H199" s="38" t="n"/>
+      <c r="I199" s="38" t="n"/>
+      <c r="J199" s="38" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/how-to-grow-curly-hair-from-bald/</t>
+        </is>
+      </c>
+      <c r="B200" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C200" s="34" t="n">
+        <v>626</v>
+      </c>
+      <c r="D200" s="35" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="E200" s="36" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="F200" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G200" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H200" s="38" t="n"/>
+      <c r="I200" s="38" t="n"/>
+      <c r="J200" s="38" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-donor-area-complete-guide/pimples-on-donor-area-after-hair-transplant/</t>
+        </is>
+      </c>
+      <c r="B201" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C201" s="34" t="n">
+        <v>619</v>
+      </c>
+      <c r="D201" s="35" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="E201" s="36" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="F201" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G201" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H201" s="38" t="n"/>
+      <c r="I201" s="38" t="n"/>
+      <c r="J201" s="38" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hydroxychloroquine-for-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B202" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C202" s="34" t="n">
+        <v>609</v>
+      </c>
+      <c r="D202" s="35" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="E202" s="36" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="F202" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G202" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H202" s="38" t="n"/>
+      <c r="I202" s="38" t="n"/>
+      <c r="J202" s="38" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/washing-your-hair-14-days-after-a-hair-transplant/</t>
+        </is>
+      </c>
+      <c r="B203" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C203" s="34" t="n">
+        <v>573</v>
+      </c>
+      <c r="D203" s="35" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+      <c r="E203" s="36" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="F203" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G203" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H203" s="38" t="n"/>
+      <c r="I203" s="38" t="n"/>
+      <c r="J203" s="38" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/bumps-on-donor-area-after-hair-transplant/</t>
+        </is>
+      </c>
+      <c r="B204" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C204" s="34" t="n">
+        <v>562</v>
+      </c>
+      <c r="D204" s="35" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="E204" s="36" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="F204" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G204" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H204" s="38" t="n"/>
+      <c r="I204" s="38" t="n"/>
+      <c r="J204" s="38" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-in-pakistan-ultimate-guide/hair-transplant-from-beard-to-head-what-to-know/</t>
+        </is>
+      </c>
+      <c r="B205" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C205" s="34" t="n">
+        <v>558</v>
+      </c>
+      <c r="D205" s="35" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="E205" s="36" t="n">
+        <v>73.77</v>
+      </c>
+      <c r="F205" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G205" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H205" s="38" t="n"/>
+      <c r="I205" s="38" t="n"/>
+      <c r="J205" s="38" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-machine-price/</t>
+        </is>
+      </c>
+      <c r="B206" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C206" s="34" t="n">
+        <v>557</v>
+      </c>
+      <c r="D206" s="35" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="E206" s="36" t="n">
+        <v>43.39</v>
+      </c>
+      <c r="F206" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G206" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H206" s="38" t="n"/>
+      <c r="I206" s="38" t="n"/>
+      <c r="J206" s="38" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/coffee-after-hair-transplant/</t>
+        </is>
+      </c>
+      <c r="B207" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C207" s="34" t="n">
+        <v>527</v>
+      </c>
+      <c r="D207" s="35" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="E207" s="36" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="F207" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G207" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H207" s="38" t="n"/>
+      <c r="I207" s="38" t="n"/>
+      <c r="J207" s="38" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-flaxseed-oil-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B208" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C208" s="34" t="n">
+        <v>524</v>
+      </c>
+      <c r="D208" s="35" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="E208" s="36" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="F208" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G208" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H208" s="38" t="n"/>
+      <c r="I208" s="38" t="n"/>
+      <c r="J208" s="38" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-donor-area-complete-guide/overharvested-donor-area-causes/</t>
+        </is>
+      </c>
+      <c r="B209" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C209" s="34" t="n">
+        <v>520</v>
+      </c>
+      <c r="D209" s="35" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="E209" s="36" t="n">
+        <v>16.97</v>
+      </c>
+      <c r="F209" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G209" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H209" s="38" t="n"/>
+      <c r="I209" s="38" t="n"/>
+      <c r="J209" s="38" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/how-does-hairline-lowering-surgery-works/</t>
+        </is>
+      </c>
+      <c r="B210" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C210" s="34" t="n">
+        <v>517</v>
+      </c>
+      <c r="D210" s="35" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="E210" s="36" t="n">
+        <v>74.63</v>
+      </c>
+      <c r="F210" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G210" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H210" s="38" t="n"/>
+      <c r="I210" s="38" t="n"/>
+      <c r="J210" s="38" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/eyebrow-transplant-cost-in-pakistan/</t>
+        </is>
+      </c>
+      <c r="B211" s="34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C211" s="34" t="n">
+        <v>492</v>
+      </c>
+      <c r="D211" s="35" t="n">
+        <v>0.06710000000000001</v>
+      </c>
+      <c r="E211" s="36" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="F211" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G211" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H211" s="38" t="n"/>
+      <c r="I211" s="38" t="n"/>
+      <c r="J211" s="38" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/does-osphena-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B212" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C212" s="34" t="n">
+        <v>474</v>
+      </c>
+      <c r="D212" s="35" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="E212" s="36" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="F212" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G212" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H212" s="38" t="n"/>
+      <c r="I212" s="38" t="n"/>
+      <c r="J212" s="38" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/is-stage-3-hair-loss-reversible/</t>
+        </is>
+      </c>
+      <c r="B213" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C213" s="34" t="n">
+        <v>472</v>
+      </c>
+      <c r="D213" s="35" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="E213" s="36" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="F213" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G213" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H213" s="38" t="n"/>
+      <c r="I213" s="38" t="n"/>
+      <c r="J213" s="38" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/what-are-hair-stones/</t>
+        </is>
+      </c>
+      <c r="B214" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C214" s="34" t="n">
+        <v>472</v>
+      </c>
+      <c r="D214" s="35" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="E214" s="36" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="F214" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G214" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H214" s="38" t="n"/>
+      <c r="I214" s="38" t="n"/>
+      <c r="J214" s="38" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-loss-after-flu/</t>
+        </is>
+      </c>
+      <c r="B215" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C215" s="34" t="n">
+        <v>471</v>
+      </c>
+      <c r="D215" s="35" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="E215" s="36" t="n">
+        <v>35.66</v>
+      </c>
+      <c r="F215" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G215" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H215" s="38" t="n"/>
+      <c r="I215" s="38" t="n"/>
+      <c r="J215" s="38" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-without-medicine/</t>
+        </is>
+      </c>
+      <c r="B216" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C216" s="34" t="n">
+        <v>466</v>
+      </c>
+      <c r="D216" s="35" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="E216" s="36" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F216" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G216" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H216" s="38" t="n"/>
+      <c r="I216" s="38" t="n"/>
+      <c r="J216" s="38" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/how-to-stop-hair-loss-from-antibiotics/</t>
+        </is>
+      </c>
+      <c r="B217" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C217" s="34" t="n">
+        <v>465</v>
+      </c>
+      <c r="D217" s="35" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="E217" s="36" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="F217" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G217" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub</t>
+        </is>
+      </c>
+      <c r="H217" s="38" t="n"/>
+      <c r="I217" s="38" t="n"/>
+      <c r="J217" s="38" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/do-dht-blockers-increase-facial-hair/</t>
+        </is>
+      </c>
+      <c r="B218" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C218" s="34" t="n">
+        <v>460</v>
+      </c>
+      <c r="D218" s="35" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+      <c r="E218" s="36" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="F218" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G218" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H218" s="38" t="n"/>
+      <c r="I218" s="38" t="n"/>
+      <c r="J218" s="38" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/how-to-wash-your-hair-in-a-bathtub/</t>
+        </is>
+      </c>
+      <c r="B219" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C219" s="34" t="n">
+        <v>454</v>
+      </c>
+      <c r="D219" s="35" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="E219" s="36" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="F219" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G219" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H219" s="38" t="n"/>
+      <c r="I219" s="38" t="n"/>
+      <c r="J219" s="38" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-extensions-itchy-after-2-weeks/</t>
+        </is>
+      </c>
+      <c r="B220" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C220" s="34" t="n">
+        <v>448</v>
+      </c>
+      <c r="D220" s="35" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="E220" s="36" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="F220" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G220" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H220" s="38" t="n"/>
+      <c r="I220" s="38" t="n"/>
+      <c r="J220" s="38" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/how-much-does-a-permanent-eyebrow-transplant-cost/</t>
+        </is>
+      </c>
+      <c r="B221" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C221" s="34" t="n">
+        <v>437</v>
+      </c>
+      <c r="D221" s="35" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="E221" s="36" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="F221" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G221" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H221" s="38" t="n"/>
+      <c r="I221" s="38" t="n"/>
+      <c r="J221" s="38" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-cost-in-pakistan/hair-transplant-cost-in-bahawalpur/</t>
+        </is>
+      </c>
+      <c r="B222" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C222" s="34" t="n">
+        <v>436</v>
+      </c>
+      <c r="D222" s="35" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="E222" s="36" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="F222" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G222" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H222" s="38" t="n"/>
+      <c r="I222" s="38" t="n"/>
+      <c r="J222" s="38" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-without-shaving-head/</t>
+        </is>
+      </c>
+      <c r="B223" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C223" s="34" t="n">
+        <v>434</v>
+      </c>
+      <c r="D223" s="35" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="E223" s="36" t="n">
+        <v>51.59</v>
+      </c>
+      <c r="F223" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G223" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H223" s="38" t="n"/>
+      <c r="I223" s="38" t="n"/>
+      <c r="J223" s="38" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/bumps-on-the-scalp-after-exercise/</t>
+        </is>
+      </c>
+      <c r="B224" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C224" s="34" t="n">
+        <v>430</v>
+      </c>
+      <c r="D224" s="35" t="n">
+        <v>0.009299999999999999</v>
+      </c>
+      <c r="E224" s="36" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="F224" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G224" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H224" s="38" t="n"/>
+      <c r="I224" s="38" t="n"/>
+      <c r="J224" s="38" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-gloss-treatment/</t>
+        </is>
+      </c>
+      <c r="B225" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C225" s="34" t="n">
+        <v>430</v>
+      </c>
+      <c r="D225" s="35" t="n">
+        <v>0.009299999999999999</v>
+      </c>
+      <c r="E225" s="36" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="F225" s="33" t="inlineStr">
+        <is>
+          <t>Hair styling/cosmetic (off-topic)</t>
+        </is>
+      </c>
+      <c r="G225" s="37" t="inlineStr">
+        <is>
+          <t>Prune (410)</t>
+        </is>
+      </c>
+      <c r="H225" s="38" t="n"/>
+      <c r="I225" s="38" t="n"/>
+      <c r="J225" s="38" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/artificial-hair-transplant-side-effects/</t>
+        </is>
+      </c>
+      <c r="B226" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C226" s="34" t="n">
+        <v>422</v>
+      </c>
+      <c r="D226" s="35" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="E226" s="36" t="n">
+        <v>31.34</v>
+      </c>
+      <c r="F226" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G226" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H226" s="38" t="n"/>
+      <c r="I226" s="38" t="n"/>
+      <c r="J226" s="38" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/burning-and-itching-sensation-scalp-after-exercising/</t>
+        </is>
+      </c>
+      <c r="B227" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C227" s="34" t="n">
+        <v>408</v>
+      </c>
+      <c r="D227" s="35" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="E227" s="36" t="n">
+        <v>29.11</v>
+      </c>
+      <c r="F227" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G227" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H227" s="38" t="n"/>
+      <c r="I227" s="38" t="n"/>
+      <c r="J227" s="38" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/beard-transplant/</t>
+        </is>
+      </c>
+      <c r="B228" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C228" s="34" t="n">
+        <v>401</v>
+      </c>
+      <c r="D228" s="35" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E228" s="36" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="F228" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G228" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H228" s="38" t="n"/>
+      <c r="I228" s="38" t="n"/>
+      <c r="J228" s="38" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/herbal-dht-blockers/</t>
+        </is>
+      </c>
+      <c r="B229" s="34" t="n">
+        <v>39</v>
+      </c>
+      <c r="C229" s="34" t="n">
+        <v>400</v>
+      </c>
+      <c r="D229" s="35" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="E229" s="36" t="n">
+        <v>14.28</v>
+      </c>
+      <c r="F229" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G229" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H229" s="38" t="n"/>
+      <c r="I229" s="38" t="n"/>
+      <c r="J229" s="38" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-cost-in-pakistan/hair-transplant-cost-in-gujrat/</t>
+        </is>
+      </c>
+      <c r="B230" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C230" s="34" t="n">
+        <v>396</v>
+      </c>
+      <c r="D230" s="35" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="E230" s="36" t="n">
+        <v>48.63</v>
+      </c>
+      <c r="F230" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G230" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H230" s="38" t="n"/>
+      <c r="I230" s="38" t="n"/>
+      <c r="J230" s="38" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/how-much-does-a-hair-test-cost/</t>
+        </is>
+      </c>
+      <c r="B231" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C231" s="34" t="n">
+        <v>383</v>
+      </c>
+      <c r="D231" s="35" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="E231" s="36" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="F231" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G231" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H231" s="38" t="n"/>
+      <c r="I231" s="38" t="n"/>
+      <c r="J231" s="38" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/exosome-vs-hair-transplant/</t>
+        </is>
+      </c>
+      <c r="B232" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C232" s="34" t="n">
+        <v>363</v>
+      </c>
+      <c r="D232" s="35" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="E232" s="36" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="F232" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G232" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H232" s="38" t="n"/>
+      <c r="I232" s="38" t="n"/>
+      <c r="J232" s="38" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-botox-cause-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B233" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C233" s="34" t="n">
+        <v>346</v>
+      </c>
+      <c r="D233" s="35" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="E233" s="36" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="F233" s="33" t="inlineStr">
+        <is>
+          <t>Drug/condition interaction farm</t>
+        </is>
+      </c>
+      <c r="G233" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
+        </is>
+      </c>
+      <c r="H233" s="38" t="n"/>
+      <c r="I233" s="38" t="n"/>
+      <c r="J233" s="38" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/sweating-after-hair-transplant/</t>
+        </is>
+      </c>
+      <c r="B234" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C234" s="34" t="n">
+        <v>344</v>
+      </c>
+      <c r="D234" s="35" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="E234" s="36" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="F234" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G234" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H234" s="38" t="n"/>
+      <c r="I234" s="38" t="n"/>
+      <c r="J234" s="38" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-cost-in-pakistan/hair-transplant-cost-in-hyderabad/</t>
+        </is>
+      </c>
+      <c r="B235" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C235" s="34" t="n">
+        <v>341</v>
+      </c>
+      <c r="D235" s="35" t="n">
+        <v>0.0176</v>
+      </c>
+      <c r="E235" s="36" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="F235" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G235" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H235" s="38" t="n"/>
+      <c r="I235" s="38" t="n"/>
+      <c r="J235" s="38" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/right-lotion-after-hair-transplant/</t>
+        </is>
+      </c>
+      <c r="B236" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C236" s="34" t="n">
+        <v>336</v>
+      </c>
+      <c r="D236" s="35" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="E236" s="36" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="F236" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G236" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H236" s="38" t="n"/>
+      <c r="I236" s="38" t="n"/>
+      <c r="J236" s="38" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/abhrs-doctors-in-pakistan/</t>
+        </is>
+      </c>
+      <c r="B237" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="C237" s="34" t="n">
+        <v>323</v>
+      </c>
+      <c r="D237" s="35" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="E237" s="36" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="F237" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G237" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H237" s="38" t="n"/>
+      <c r="I237" s="38" t="n"/>
+      <c r="J237" s="38" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-cloning-pakistan-2025/</t>
+        </is>
+      </c>
+      <c r="B238" s="34" t="n">
+        <v>27</v>
+      </c>
+      <c r="C238" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="D238" s="35" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E238" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="F238" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G238" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H238" s="38" t="n"/>
+      <c r="I238" s="38" t="n"/>
+      <c r="J238" s="38" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/can-chest-hair-be-transplanted-to-head/</t>
+        </is>
+      </c>
+      <c r="B239" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C239" s="34" t="n">
+        <v>285</v>
+      </c>
+      <c r="D239" s="35" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="E239" s="36" t="n">
+        <v>64.54000000000001</v>
+      </c>
+      <c r="F239" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G239" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H239" s="38" t="n"/>
+      <c r="I239" s="38" t="n"/>
+      <c r="J239" s="38" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hairline-advancement-surgery-cost-in-pakistan/</t>
+        </is>
+      </c>
+      <c r="B240" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="C240" s="34" t="n">
+        <v>277</v>
+      </c>
+      <c r="D240" s="35" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="E240" s="36" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="F240" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G240" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H240" s="38" t="n"/>
+      <c r="I240" s="38" t="n"/>
+      <c r="J240" s="38" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-package-turkey/</t>
+        </is>
+      </c>
+      <c r="B241" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C241" s="34" t="n">
+        <v>265</v>
+      </c>
+      <c r="D241" s="35" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="E241" s="36" t="n">
+        <v>79.04000000000001</v>
+      </c>
+      <c r="F241" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G241" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H241" s="38" t="n"/>
+      <c r="I241" s="38" t="n"/>
+      <c r="J241" s="38" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/finasteride-spray-for-hair-loss/</t>
+        </is>
+      </c>
+      <c r="B242" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C242" s="34" t="n">
+        <v>264</v>
+      </c>
+      <c r="D242" s="35" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="E242" s="36" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="F242" s="33" t="inlineStr">
+        <is>
+          <t>Finasteride micro-pages</t>
+        </is>
+      </c>
+      <c r="G242" s="37" t="inlineStr">
+        <is>
+          <t>Consolidate into one pillar guide + FAQ</t>
+        </is>
+      </c>
+      <c r="H242" s="38" t="n"/>
+      <c r="I242" s="38" t="n"/>
+      <c r="J242" s="38" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-donor-area-complete-guide/fue-donor-area-after-two-weeks-s-appearance-amp-expert-care/</t>
+        </is>
+      </c>
+      <c r="B243" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C243" s="34" t="n">
+        <v>260</v>
+      </c>
+      <c r="D243" s="35" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="E243" s="36" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="F243" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G243" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H243" s="38" t="n"/>
+      <c r="I243" s="38" t="n"/>
+      <c r="J243" s="38" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-age-60/</t>
+        </is>
+      </c>
+      <c r="B244" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C244" s="34" t="n">
+        <v>225</v>
+      </c>
+      <c r="D244" s="35" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="E244" s="36" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="F244" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G244" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H244" s="38" t="n"/>
+      <c r="I244" s="38" t="n"/>
+      <c r="J244" s="38" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/partial-hair-system/</t>
+        </is>
+      </c>
+      <c r="B245" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C245" s="34" t="n">
+        <v>195</v>
+      </c>
+      <c r="D245" s="35" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="E245" s="36" t="n">
+        <v>50.89</v>
+      </c>
+      <c r="F245" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G245" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H245" s="38" t="n"/>
+      <c r="I245" s="38" t="n"/>
+      <c r="J245" s="38" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-cost-in-pakistan/hair-transplant-cost-in-quetta/</t>
+        </is>
+      </c>
+      <c r="B246" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C246" s="34" t="n">
+        <v>187</v>
+      </c>
+      <c r="D246" s="35" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="E246" s="36" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="F246" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G246" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H246" s="38" t="n"/>
+      <c r="I246" s="38" t="n"/>
+      <c r="J246" s="38" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/privacy-policy/</t>
+        </is>
+      </c>
+      <c r="B247" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C247" s="34" t="n">
+        <v>168</v>
+      </c>
+      <c r="D247" s="35" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="E247" s="36" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="F247" s="33" t="inlineStr">
+        <is>
+          <t>Core site page</t>
+        </is>
+      </c>
+      <c r="G247" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H247" s="38" t="n"/>
+      <c r="I247" s="38" t="n"/>
+      <c r="J247" s="38" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/how-many-grafts-for-eyebrow-transplant/</t>
+        </is>
+      </c>
+      <c r="B248" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C248" s="34" t="n">
+        <v>163</v>
+      </c>
+      <c r="D248" s="35" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="E248" s="36" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="F248" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G248" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H248" s="38" t="n"/>
+      <c r="I248" s="38" t="n"/>
+      <c r="J248" s="38" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-transplant-without-donor-area/</t>
+        </is>
+      </c>
+      <c r="B249" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C249" s="34" t="n">
+        <v>158</v>
+      </c>
+      <c r="D249" s="35" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="E249" s="36" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="F249" s="33" t="inlineStr">
+        <is>
+          <t>Post-op care</t>
+        </is>
+      </c>
+      <c r="G249" s="37" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="H249" s="38" t="n"/>
+      <c r="I249" s="38" t="n"/>
+      <c r="J249" s="38" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/eyebrow-transplant/best-eyebrow-transplant-surgeon/</t>
+        </is>
+      </c>
+      <c r="B250" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C250" s="34" t="n">
+        <v>114</v>
+      </c>
+      <c r="D250" s="35" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="E250" s="36" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="F250" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G250" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H250" s="38" t="n"/>
+      <c r="I250" s="38" t="n"/>
+      <c r="J250" s="38" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/exosome-hair-treatment-benefits/</t>
+        </is>
+      </c>
+      <c r="B251" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C251" s="34" t="n">
+        <v>73</v>
+      </c>
+      <c r="D251" s="35" t="n">
+        <v>0.0411</v>
+      </c>
+      <c r="E251" s="36" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="F251" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G251" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H251" s="38" t="n"/>
+      <c r="I251" s="38" t="n"/>
+      <c r="J251" s="38" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/hair-grafting-procedure/</t>
+        </is>
+      </c>
+      <c r="B252" s="34" t="n">
+        <v>26</v>
+      </c>
+      <c r="C252" s="34" t="n">
+        <v>70</v>
+      </c>
+      <c r="D252" s="35" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="E252" s="36" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="F252" s="33" t="inlineStr">
+        <is>
+          <t>Core procedure/commercial</t>
+        </is>
+      </c>
+      <c r="G252" s="37" t="inlineStr">
+        <is>
+          <t>Keep &amp; strengthen</t>
+        </is>
+      </c>
+      <c r="H252" s="38" t="n"/>
+      <c r="I252" s="38" t="n"/>
+      <c r="J252" s="38" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/tag/curling/</t>
+        </is>
+      </c>
+      <c r="B253" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C253" s="34" t="n">
+        <v>43</v>
+      </c>
+      <c r="D253" s="35" t="n">
+        <v>0.1163</v>
+      </c>
+      <c r="E253" s="36" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="F253" s="33" t="inlineStr">
+        <is>
+          <t>Thin archive/technical</t>
+        </is>
+      </c>
+      <c r="G253" s="37" t="inlineStr">
+        <is>
+          <t>See TECH-03/14 — fix via noindex, not a content decision</t>
+        </is>
+      </c>
+      <c r="H253" s="38" t="n"/>
+      <c r="I253" s="38" t="n"/>
+      <c r="J253" s="38" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/tag/dht-level/</t>
+        </is>
+      </c>
+      <c r="B254" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C254" s="34" t="n">
+        <v>39</v>
+      </c>
+      <c r="D254" s="35" t="n">
+        <v>0.1026</v>
+      </c>
+      <c r="E254" s="36" t="n">
+        <v>34.85</v>
+      </c>
+      <c r="F254" s="33" t="inlineStr">
+        <is>
+          <t>Thin archive/technical</t>
+        </is>
+      </c>
+      <c r="G254" s="37" t="inlineStr">
+        <is>
+          <t>See TECH-03/14 — fix via noindex, not a content decision</t>
+        </is>
+      </c>
+      <c r="H254" s="38" t="n"/>
+      <c r="I254" s="38" t="n"/>
+      <c r="J254" s="38" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="33" t="inlineStr">
+        <is>
+          <t>https://drranairfan.com/blog/77/</t>
+        </is>
+      </c>
+      <c r="B255" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C255" s="34" t="n">
+        <v>24</v>
+      </c>
+      <c r="D255" s="35" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="E255" s="36" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="F255" s="33" t="inlineStr">
+        <is>
+          <t>Technical cleanup</t>
+        </is>
+      </c>
+      <c r="G255" s="37" t="inlineStr">
+        <is>
+          <t>Investigate/410</t>
+        </is>
+      </c>
+      <c r="H255" s="38" t="n"/>
+      <c r="I255" s="38" t="n"/>
+      <c r="J255" s="38" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="H6:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Keep,Keep &amp; strengthen,Consolidate,Merge/301,Prune/410,Rework,Needs review"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I6:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
+++ b/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
@@ -56193,7 +56193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="23" min="1" max="1"/>
@@ -56486,6 +56486,43 @@
         </is>
       </c>
       <c r="G11" s="32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="120" customHeight="1" s="23">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>On Page SEO Issue</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>OP-02 (4 duplicate pairs)</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="inlineStr">
+        <is>
+          <t>Finalized the redirect direction for the 4 duplicate/near-duplicate pairs found in the OP-02 blog audit, and drafted the actual redirect rules ready to apply.</t>
+        </is>
+      </c>
+      <c r="E12" s="31" t="inlineStr">
+        <is>
+          <t>Set Final Decision/Notes in the 'OP-02 Blog Audit' tab for all 8 rows in the 4 pairs - each winner marked Keep (with why), each loser marked Merge/301 with the explicit destination URL. Wrote both a Rank Math Redirections table and raw .htaccess RewriteRule syntax in docs/seo/technical/OP-02-duplicate-redirects.md, with the merge-content-first caveat repeated. Did not apply any redirect - needs WordPress/hosting access this agent doesn't have.</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>DrRanaIrfanSEOIssueTracker.xlsx tab 'OP-02 Blog Audit' (8 rows); docs/seo/technical/OP-02-duplicate-redirects.md</t>
+        </is>
+      </c>
+      <c r="G12" s="32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -56512,7 +56549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J255"/>
+  <dimension ref="A1:J259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="46" customWidth="1" style="23" min="1" max="1"/>
@@ -56917,9 +56954,17 @@
           <t>Merge/301</t>
         </is>
       </c>
-      <c r="H14" s="38" t="n"/>
+      <c r="H14" s="38" t="inlineStr">
+        <is>
+          <t>Merge/301</t>
+        </is>
+      </c>
       <c r="I14" s="38" t="n"/>
-      <c r="J14" s="38" t="n"/>
+      <c r="J14" s="38" t="inlineStr">
+        <is>
+          <t>301 THIS -&gt; /how-much-does-hair-weigh/ (keep the winner: 48 clicks/90d vs 36, better position 6.1 vs 7.1 despite more impressions here). Merge any unique content into the winner first. Redirect rule drafted in docs/seo/technical/OP-02-duplicate-redirects.md.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="33" t="inlineStr">
@@ -57109,9 +57154,17 @@
           <t>Merge/301</t>
         </is>
       </c>
-      <c r="H20" s="38" t="n"/>
+      <c r="H20" s="38" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
       <c r="I20" s="38" t="n"/>
-      <c r="J20" s="38" t="n"/>
+      <c r="J20" s="38" t="inlineStr">
+        <is>
+          <t>KEEP as the 301 destination for /does-hair-weigh-anything/ (48 clicks/90d vs 36, better position).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="33" t="inlineStr">
@@ -58773,9 +58826,17 @@
           <t>Merge/301</t>
         </is>
       </c>
-      <c r="H72" s="38" t="n"/>
+      <c r="H72" s="38" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
       <c r="I72" s="38" t="n"/>
-      <c r="J72" s="38" t="n"/>
+      <c r="J72" s="38" t="inlineStr">
+        <is>
+          <t>KEEP as the 301 destination for /does-zyn-cause-hair-loss/ (50 clicks/90d vs 25 - the '-2' URL is the stronger one).</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="33" t="inlineStr">
@@ -59285,9 +59346,17 @@
           <t>Merge/301</t>
         </is>
       </c>
-      <c r="H88" s="38" t="n"/>
+      <c r="H88" s="38" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
       <c r="I88" s="38" t="n"/>
-      <c r="J88" s="38" t="n"/>
+      <c r="J88" s="38" t="inlineStr">
+        <is>
+          <t>KEEP as the 301 destination for /can-low-blood-pressure-cause-hair-loss/ (79 clicks/90d vs 8 - clear winner).</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="33" t="inlineStr">
@@ -59733,9 +59802,17 @@
           <t>Merge/301</t>
         </is>
       </c>
-      <c r="H102" s="38" t="n"/>
+      <c r="H102" s="38" t="inlineStr">
+        <is>
+          <t>Merge/301</t>
+        </is>
+      </c>
       <c r="I102" s="38" t="n"/>
-      <c r="J102" s="38" t="n"/>
+      <c r="J102" s="38" t="inlineStr">
+        <is>
+          <t>301 THIS -&gt; /does-zyn-cause-hair-loss-2/ (keep the winner: 50 clicks/90d vs 25, despite the uglier '-2' slug - don't rename it, that just creates another redirect to manage). Merge any unique content into the winner first. Redirect rule drafted in docs/seo/technical/OP-02-duplicate-redirects.md.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="33" t="inlineStr">
@@ -59861,9 +59938,17 @@
           <t>Merge/301</t>
         </is>
       </c>
-      <c r="H106" s="38" t="n"/>
+      <c r="H106" s="38" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
       <c r="I106" s="38" t="n"/>
-      <c r="J106" s="38" t="n"/>
+      <c r="J106" s="38" t="inlineStr">
+        <is>
+          <t>KEEP as the 301 destination for /title-can-progesterone-cause-hair-loss/ (15 clicks/90d vs 6 - clear winner).</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="33" t="inlineStr">
@@ -60853,9 +60938,17 @@
           <t>Merge/301</t>
         </is>
       </c>
-      <c r="H137" s="38" t="n"/>
+      <c r="H137" s="38" t="inlineStr">
+        <is>
+          <t>Merge/301</t>
+        </is>
+      </c>
       <c r="I137" s="38" t="n"/>
-      <c r="J137" s="38" t="n"/>
+      <c r="J137" s="38" t="inlineStr">
+        <is>
+          <t>301 THIS -&gt; /progesterone-female-hair-loss/ (keep the winner: 15 clicks/90d vs 6; this slug also still carries a leftover 'title-' prefix from a bad import). Merge any unique content into the winner first. Redirect rule drafted in docs/seo/technical/OP-02-duplicate-redirects.md.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="33" t="inlineStr">
@@ -61653,9 +61746,17 @@
           <t>Merge/301</t>
         </is>
       </c>
-      <c r="H162" s="38" t="n"/>
+      <c r="H162" s="38" t="inlineStr">
+        <is>
+          <t>Merge/301</t>
+        </is>
+      </c>
       <c r="I162" s="38" t="n"/>
-      <c r="J162" s="38" t="n"/>
+      <c r="J162" s="38" t="inlineStr">
+        <is>
+          <t>301 THIS -&gt; /low-blood-pressure-and-hair-loss/ (keep the winner: 79 clicks/90d vs 8, position 10.1 vs 22.8). Merge any unique content into the winner first. Redirect rule drafted in docs/seo/technical/OP-02-duplicate-redirects.md.</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="33" t="inlineStr">
@@ -64633,6 +64734,10 @@
       <c r="I255" s="38" t="n"/>
       <c r="J255" s="38" t="n"/>
     </row>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>

--- a/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
+++ b/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
@@ -56193,7 +56193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="23" min="1" max="1"/>
@@ -56523,6 +56523,43 @@
         </is>
       </c>
       <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="140" customHeight="1" s="23">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>On Page SEO Issue</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>OP-02 (full duplicate re-scan)</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>Ran a systematic pairwise similarity scan across all 250 blog URLs (not just within-cluster spot-checks) after the user asked whether the original 4 duplicate pairs were the complete list.</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
+        <is>
+          <t>Found 3 more genuine duplicates the original pass missed - same topic published twice under different URL structures (standalone vs nested in a guide series): /hair-transplant-cost-in-islamabad/, /hair-transplant-donor-area-complete-guide/.../pimples-on-donor-area-after-hair-transplant/, /foods-that-increase-dht/. Set Final Decision/Notes for all 6 rows (3 winners, 3 losers with explicit destinations). Also surfaced a real keyword-cannibalization pair that is NOT a simple duplicate - /updated-hair-transplant-prices-in-pakistan/ vs /hair-transplant-cost-in-pakistan/ - flagged as Needs review instead of Merge/301 since the weaker page is also the parent hub for city pricing subpages. Updated docs/seo/technical/OP-02-duplicate-redirects.md with the 3 new redirect rules. Total duplicate pairs resolved: 7 (was 4).</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>DrRanaIrfanSEOIssueTracker.xlsx tab 'OP-02 Blog Audit' (6 rows); docs/seo/technical/OP-02-duplicate-redirects.md</t>
+        </is>
+      </c>
+      <c r="G13" s="32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -57058,9 +57095,17 @@
           <t>Keep &amp; strengthen</t>
         </is>
       </c>
-      <c r="H17" s="38" t="n"/>
+      <c r="H17" s="38" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
       <c r="I17" s="38" t="n"/>
-      <c r="J17" s="38" t="n"/>
+      <c r="J17" s="38" t="inlineStr">
+        <is>
+          <t>KEYWORD CANNIBALIZATION, not a simple duplicate - do not 301 this pair. /updated-hair-transplant-prices-in-pakistan/ (214 clicks/90d, pos 11.0) and /hair-transplant-cost-in-pakistan/ (12 clicks/90d, pos 51.1) compete for the same pricing intent, but the weaker page is also the parent hub for the city-specific pricing subpages (Islamabad, Lahore, Karachi, etc.) - redirecting it away would orphan those. Needs a content decision: make updated-hair-transplant-prices-in-pakistan the primary pricing pillar and link city pages from there, or merge its content into the hub instead.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="33" t="inlineStr">
@@ -57962,9 +58007,17 @@
           <t>Consolidate into FAQ hub, or prune if zero plausible relevance</t>
         </is>
       </c>
-      <c r="H45" s="38" t="n"/>
+      <c r="H45" s="38" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
       <c r="I45" s="38" t="n"/>
-      <c r="J45" s="38" t="n"/>
+      <c r="J45" s="38" t="inlineStr">
+        <is>
+          <t>KEEP as the 301 destination for /foods-that-increase-dht/ (64 clicks/90d vs 23).</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="33" t="inlineStr">
@@ -58506,9 +58559,17 @@
           <t>Keep &amp; strengthen</t>
         </is>
       </c>
-      <c r="H62" s="38" t="n"/>
+      <c r="H62" s="38" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
       <c r="I62" s="38" t="n"/>
-      <c r="J62" s="38" t="n"/>
+      <c r="J62" s="38" t="inlineStr">
+        <is>
+          <t>KEYWORD CANNIBALIZATION, not a simple duplicate - do not 301 this pair. /updated-hair-transplant-prices-in-pakistan/ (214 clicks/90d, pos 11.0) and /hair-transplant-cost-in-pakistan/ (12 clicks/90d, pos 51.1) compete for the same pricing intent, but the weaker page is also the parent hub for the city-specific pricing subpages (Islamabad, Lahore, Karachi, etc.) - redirecting it away would orphan those. Needs a content decision: make updated-hair-transplant-prices-in-pakistan the primary pricing pillar and link city pages from there, or merge its content into the hub instead.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="33" t="inlineStr">
@@ -58730,9 +58791,17 @@
           <t>Consolidate into a single DHT/diet FAQ section</t>
         </is>
       </c>
-      <c r="H69" s="38" t="n"/>
+      <c r="H69" s="38" t="inlineStr">
+        <is>
+          <t>Merge/301</t>
+        </is>
+      </c>
       <c r="I69" s="38" t="n"/>
-      <c r="J69" s="38" t="n"/>
+      <c r="J69" s="38" t="inlineStr">
+        <is>
+          <t>301 THIS -&gt; /foods-that-increase-dht-production/ (winner: 64 clicks/90d vs 23, position 11.4 vs 22.2). Found in the follow-up full pairwise duplicate scan.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="33" t="inlineStr">
@@ -59874,9 +59943,17 @@
           <t>Keep &amp; strengthen</t>
         </is>
       </c>
-      <c r="H104" s="38" t="n"/>
+      <c r="H104" s="38" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
       <c r="I104" s="38" t="n"/>
-      <c r="J104" s="38" t="n"/>
+      <c r="J104" s="38" t="inlineStr">
+        <is>
+          <t>KEEP as the 301 destination for the standalone /hair-transplant-cost-in-islamabad/ duplicate (35 clicks/90d vs 4).</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="33" t="inlineStr">
@@ -60522,9 +60599,17 @@
           <t>Keep</t>
         </is>
       </c>
-      <c r="H124" s="38" t="n"/>
+      <c r="H124" s="38" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
       <c r="I124" s="38" t="n"/>
-      <c r="J124" s="38" t="n"/>
+      <c r="J124" s="38" t="inlineStr">
+        <is>
+          <t>KEEP as the 301 destination for the nested duplicate in the donor-area-complete-guide series (16 clicks/90d vs 3).</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="33" t="inlineStr">
@@ -62362,9 +62447,17 @@
           <t>Keep &amp; strengthen</t>
         </is>
       </c>
-      <c r="H181" s="38" t="n"/>
+      <c r="H181" s="38" t="inlineStr">
+        <is>
+          <t>Merge/301</t>
+        </is>
+      </c>
       <c r="I181" s="38" t="n"/>
-      <c r="J181" s="38" t="n"/>
+      <c r="J181" s="38" t="inlineStr">
+        <is>
+          <t>301 THIS -&gt; /hair-transplant-cost-in-pakistan/hair-transplant-cost-in-islamabad/ (nested version wins: 35 clicks/90d vs 4, position 30 vs 57). Found in the follow-up full pairwise duplicate scan, not the original spot-check.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="33" t="inlineStr">
@@ -63002,9 +63095,17 @@
           <t>Keep</t>
         </is>
       </c>
-      <c r="H201" s="38" t="n"/>
+      <c r="H201" s="38" t="inlineStr">
+        <is>
+          <t>Merge/301</t>
+        </is>
+      </c>
       <c r="I201" s="38" t="n"/>
-      <c r="J201" s="38" t="n"/>
+      <c r="J201" s="38" t="inlineStr">
+        <is>
+          <t>301 THIS -&gt; /pimples-on-the-donor-area-after-hair-transplant/ (standalone version wins: 16 clicks/90d vs 3, position 8.5 vs 16.8). Found in the follow-up full pairwise duplicate scan.</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="33" t="inlineStr">

--- a/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
+++ b/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
@@ -56193,7 +56193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="23" min="1" max="1"/>
@@ -56560,6 +56560,43 @@
         </is>
       </c>
       <c r="G13" s="32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="150" customHeight="1" s="23">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>On Page SEO Issue</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="inlineStr">
+        <is>
+          <t>OP-02 (pricing-page cannibalization)</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="inlineStr">
+        <is>
+          <t>Resolved the /hair-transplant-cost-in-pakistan/ vs /updated-hair-transplant-prices-in-pakistan/ cannibalization that was flagged as Needs review rather than acted on.</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="inlineStr">
+        <is>
+          <t>Corrected an earlier over-cautious read: a Rank Math Exact-match redirect on the hub URL does not affect its 12 nested city-specific subpages (Exact match doesn't prefix-match), so redirecting the hub itself is safe. Cross-referenced OP-09's own recommended fix, which already treats /updated-hair-transplant-prices-in-pakistan/ as the canonical pricing page - used that as the deciding factor rather than picking whichever page currently ranks higher. Decision: 301 /hair-transplant-cost-in-pakistan/ -&gt; /updated-hair-transplant-prices-in-pakistan/, then add internal links from the surviving page to all 12 city subpages (list with real GSC data prepared). Updated the tracker (both rows resolved from Needs review) and docs/seo/technical/OP-02-duplicate-redirects.md with the 8th redirect and the internal-linking task. Not applied - needs WordPress access, and someone should sanity-check both pages' actual content for anything unique worth merging before the redirect goes live.</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>DrRanaIrfanSEOIssueTracker.xlsx tab 'OP-02 Blog Audit' (2 rows); docs/seo/technical/OP-02-duplicate-redirects.md</t>
+        </is>
+      </c>
+      <c r="G14" s="32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -57097,13 +57134,13 @@
       </c>
       <c r="H17" s="38" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Keep &amp; strengthen</t>
         </is>
       </c>
       <c r="I17" s="38" t="n"/>
       <c r="J17" s="38" t="inlineStr">
         <is>
-          <t>KEYWORD CANNIBALIZATION, not a simple duplicate - do not 301 this pair. /updated-hair-transplant-prices-in-pakistan/ (214 clicks/90d, pos 11.0) and /hair-transplant-cost-in-pakistan/ (12 clicks/90d, pos 51.1) compete for the same pricing intent, but the weaker page is also the parent hub for the city-specific pricing subpages (Islamabad, Lahore, Karachi, etc.) - redirecting it away would orphan those. Needs a content decision: make updated-hair-transplant-prices-in-pakistan the primary pricing pillar and link city pages from there, or merge its content into the hub instead.</t>
+          <t>RESOLVED as the surviving pricing pillar - receives the 301 from /hair-transplant-cost-in-pakistan/. Needs internal links added to all 12 city-specific pricing subpages (currently only linked from the hub page being retired) - see docs/seo/technical/OP-02-duplicate-redirects.md for the ready list. Also check its content against /hair-transplant-cost-in-pakistan/ for anything worth merging in before that page redirects here.</t>
         </is>
       </c>
     </row>
@@ -58561,13 +58598,13 @@
       </c>
       <c r="H62" s="38" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Merge/301</t>
         </is>
       </c>
       <c r="I62" s="38" t="n"/>
       <c r="J62" s="38" t="inlineStr">
         <is>
-          <t>KEYWORD CANNIBALIZATION, not a simple duplicate - do not 301 this pair. /updated-hair-transplant-prices-in-pakistan/ (214 clicks/90d, pos 11.0) and /hair-transplant-cost-in-pakistan/ (12 clicks/90d, pos 51.1) compete for the same pricing intent, but the weaker page is also the parent hub for the city-specific pricing subpages (Islamabad, Lahore, Karachi, etc.) - redirecting it away would orphan those. Needs a content decision: make updated-hair-transplant-prices-in-pakistan the primary pricing pillar and link city pages from there, or merge its content into the hub instead.</t>
+          <t>RESOLVED: 301 THIS -&gt; /updated-hair-transplant-prices-in-pakistan/. A Rank Math 'Exact' match redirect on this one URL does NOT affect the 12 city-specific subpages nested under this path (Exact match doesn't prefix-match, e.g. .../hair-transplant-cost-in-multan/ is untouched) - they stay exactly where they are. OP-09's own recommended fix already treats /updated-hair-transplant-prices-in-pakistan/ as the canonical pricing destination ('link to it from the homepage'), which is the deciding factor over just going with whichever page currently ranks higher. Before redirecting: check this page's content for anything (pricing table, FAQ) not already on the destination page and merge it in first.</t>
         </is>
       </c>
     </row>

--- a/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
+++ b/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
@@ -947,11 +947,15 @@
       <c r="H8" s="14" t="n"/>
       <c r="I8" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J8" s="16" t="n"/>
-      <c r="K8" s="14" t="n"/>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>The 3 named examples already have dispositions in the 'OP-02 Blog Audit' tab (prune/consolidate) - nothing new there. Computed this row's actual signature (position &lt;=10, impressions &gt;=2000, CTR &lt;=1.5%) across all 250 URLs: 59 match it, mostly already covered by OP-02. New finding: 6 of those 59 are pages marked 'Keep' in OP-02, including /can-hair-grow-back-after-thinning/ - position 5.2 but 0.02% CTR (4 clicks from 16,669 impressions), the worst zero-click case on the site. These need active rewriting (something a snippet can't reproduce: photo, tool, specific next step), not just 'keep as-is'. Full detail and the reframing guidance in docs/seo/content/OP-03-zero-click-audit.md, which also connects this row's 'redirect effort to commercial/medical-tourism intent' instruction forward to OP-04 and OP-10 as the two named gaps that fit.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="34.5" customHeight="1" s="23">
       <c r="A9" s="17" t="inlineStr">
@@ -56193,7 +56197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="23" min="1" max="1"/>
@@ -56597,6 +56601,43 @@
         </is>
       </c>
       <c r="G14" s="32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="150" customHeight="1" s="23">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>On Page SEO Issue</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>OP-03</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>Worked the zero-click / AI-Overview-absorption item with a computed signature rather than just the 3 named examples.</t>
+        </is>
+      </c>
+      <c r="E15" s="31" t="inlineStr">
+        <is>
+          <t>Confirmed OP-03's 3 named URLs already have dispositions in the OP-02 Blog Audit tab. Computed the actual zero-click signature (position &lt;=10, impressions &gt;=2000, CTR &lt;=1.5%) across all 250 URLs: 59 match it, validating most of OP-02's prune/consolidate calls. New finding not previously surfaced: 6 of those 59 are pages OP-02 marked Keep, including /can-hair-grow-back-after-thinning/ (pos 5.2, 0.02% CTR, the worst zero-click case site-wide) - these need active rewriting to compete with AI Overviews, not passive retention. Wrote docs/seo/content/OP-03-zero-click-audit.md with the rewrite direction and priority order, and connected OP-03's 'redirect effort to commercial/medical-tourism intent' instruction to OP-04 (International Patients hub) and OP-10 (IFI technique page) as the two named content gaps that fit. Enriched the 6 affected rows in the OP-02 Blog Audit tab with this follow-up note. Not yet rewritten - needs WordPress access and clinic input on the self-assessment reframing.</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>docs/seo/content/OP-03-zero-click-audit.md; On Page SEO Issue tab row OP-03; OP-02 Blog Audit tab (6 rows enriched)</t>
+        </is>
+      </c>
+      <c r="G15" s="32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -57310,7 +57351,11 @@
       </c>
       <c r="H22" s="38" t="n"/>
       <c r="I22" s="38" t="n"/>
-      <c r="J22" s="38" t="n"/>
+      <c r="J22" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | OP-03 FOLLOW-UP: zero-click signature despite good position (8.1, 0.75% CTR). Priority rewrite target - see docs/seo/content/OP-03-zero-click-audit.md.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="33" t="inlineStr">
@@ -57374,7 +57419,11 @@
       </c>
       <c r="H24" s="38" t="n"/>
       <c r="I24" s="38" t="n"/>
-      <c r="J24" s="38" t="n"/>
+      <c r="J24" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | OP-03 FOLLOW-UP: worst zero-click case on the site - pos 5.2 but 0.02% CTR (4 clicks/16,669 impr). Reframe from definitional ('can hair grow back') to self-assessment ('is MY hair loss reversible' - Norwood stage, book a consultation) - see docs/seo/content/OP-03-zero-click-audit.md.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="33" t="inlineStr">
@@ -58118,7 +58167,11 @@
       </c>
       <c r="H47" s="38" t="n"/>
       <c r="I47" s="38" t="n"/>
-      <c r="J47" s="38" t="n"/>
+      <c r="J47" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | OP-03 FOLLOW-UP: zero-click signature (pos 5.9, 0.13% CTR) - lower priority than the 3 core/commercial rows, see docs/seo/content/OP-03-zero-click-audit.md.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="33" t="inlineStr">
@@ -58310,7 +58363,11 @@
       </c>
       <c r="H53" s="38" t="n"/>
       <c r="I53" s="38" t="n"/>
-      <c r="J53" s="38" t="n"/>
+      <c r="J53" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | OP-03 FOLLOW-UP: zero-click signature noted (pos 5.7, 1.36% CTR) - lower priority than the 3 core/commercial rows.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="33" t="inlineStr">
@@ -59590,7 +59647,11 @@
       </c>
       <c r="H92" s="38" t="n"/>
       <c r="I92" s="38" t="n"/>
-      <c r="J92" s="38" t="n"/>
+      <c r="J92" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | OP-03 FOLLOW-UP: zero-click signature despite good position (8.1, 1.06% CTR). Priority rewrite target - see docs/seo/content/OP-03-zero-click-audit.md.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="33" t="inlineStr">
@@ -60644,7 +60705,7 @@
       <c r="I124" s="38" t="n"/>
       <c r="J124" s="38" t="inlineStr">
         <is>
-          <t>KEEP as the 301 destination for the nested duplicate in the donor-area-complete-guide series (16 clicks/90d vs 3).</t>
+          <t>KEEP as the 301 destination for the nested duplicate in the donor-area-complete-guide series (16 clicks/90d vs 3). | OP-03 FOLLOW-UP: zero-click signature noted (pos 8.5, 0.79% CTR) - lower priority than the 3 core/commercial rows.</t>
         </is>
       </c>
     </row>

--- a/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
+++ b/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
@@ -655,7 +655,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K1000"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="6" customWidth="1" style="23" min="1" max="1"/>
     <col width="38" customWidth="1" style="23" min="2" max="2"/>
@@ -14446,7 +14446,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K1000"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="6" customWidth="1" style="23" min="1" max="1"/>
     <col width="38" customWidth="1" style="23" min="2" max="2"/>
@@ -28141,7 +28141,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K1000"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="6" customWidth="1" style="23" min="1" max="1"/>
     <col width="38" customWidth="1" style="23" min="2" max="2"/>
@@ -42000,7 +42000,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I331"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5" customWidth="1" style="23" min="1" max="1"/>
     <col width="34" customWidth="1" style="23" min="2" max="2"/>
@@ -56197,8 +56197,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="23" min="1" max="1"/>
     <col width="18" customWidth="1" style="23" min="2" max="2"/>
@@ -56638,6 +56638,43 @@
         </is>
       </c>
       <c r="G15" s="32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="130" customHeight="1" s="23">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>On Page SEO Issue</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>OP-03 (fix walkthrough)</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>Wrote the actual field-by-field fix for the 3 priority zero-click pages, so the finding converts into something executable in wp-admin rather than staying analysis.</t>
+        </is>
+      </c>
+      <c r="E16" s="31" t="inlineStr">
+        <is>
+          <t>docs/seo/content/OP-03-fix-walkthrough.md: ready-to-paste SEO Title + Meta Description (via Rank Math's per-post snippet editor) and an on-page self-assessment/CTA block to add near the top (not a rewrite - these pages already rank well, so existing content stays, new content is additive) for /can-hair-grow-back-after-thinning/, /hair-prp-price-in-pakistan/, and /scalp-reduction-surgery/. Lighter guidance for the 3 lower-priority post-op pages, with a different CTA angle (WhatsApp post-op support, not a new consultation) since those readers have usually already had the procedure. Not applied - needs WordPress access.</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>docs/seo/content/OP-03-fix-walkthrough.md</t>
+        </is>
+      </c>
+      <c r="G16" s="32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -56664,8 +56701,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J259"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:J255"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" style="23" min="1" max="1"/>
     <col width="10" customWidth="1" style="23" min="2" max="2"/>
@@ -64933,10 +64970,6 @@
       <c r="I255" s="38" t="n"/>
       <c r="J255" s="38" t="n"/>
     </row>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>

--- a/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
+++ b/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
@@ -655,7 +655,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K1000"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" style="23" min="1" max="1"/>
     <col width="38" customWidth="1" style="23" min="2" max="2"/>
@@ -996,11 +996,15 @@
       <c r="H9" s="14" t="n"/>
       <c r="I9" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J9" s="16" t="n"/>
-      <c r="K9" s="14" t="n"/>
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>Full page draft in docs/seo/content/OP-04-international-patients-page.md: visa/entry requirements (researched - short-term 3mo/long-term 1yr medical visa, document list), a sourced cost-comparison table (UK/UAE/Saudi/US per-graft and package pricing vs this clinic's own PKR 70/graft and PKR 100k-400k band from OP-09), a suggested day-by-day timeline, virtual consultation section, and FAQ candidates. IMPORTANT OPERATIONAL FLAG, not just content: Pakistan's medical visa requires a consent letter from a hospital on the Ministry of National Health Services ENLISTED HOSPITALS list - confirm Vagus Surgery Clinic is on that list before this page promises visa support, independent of the SEO work. Accommodation and airport transfer sections left as explicit placeholders - no clinic partnership/service details were available to confirm, so nothing was invented. Not published - needs WordPress access and those 3 confirmations (enlisted-hospital status, accommodation, airport transfer).</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="34.5" customHeight="1" s="23">
       <c r="A10" s="11" t="inlineStr">
@@ -14446,7 +14450,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K1000"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" style="23" min="1" max="1"/>
     <col width="38" customWidth="1" style="23" min="2" max="2"/>
@@ -28141,7 +28145,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K1000"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" style="23" min="1" max="1"/>
     <col width="38" customWidth="1" style="23" min="2" max="2"/>
@@ -42000,7 +42004,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I331"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" style="23" min="1" max="1"/>
     <col width="34" customWidth="1" style="23" min="2" max="2"/>
@@ -56197,8 +56201,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="23" min="1" max="1"/>
     <col width="18" customWidth="1" style="23" min="2" max="2"/>
@@ -56675,6 +56679,43 @@
         </is>
       </c>
       <c r="G16" s="32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="150" customHeight="1" s="23">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>On Page SEO Issue</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>OP-04</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>Drafted the missing International Patients hub page from scratch, researching real external facts rather than estimating them.</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>Researched Pakistan's medical visa process and current hair transplant pricing in the UK, UAE, Saudi Arabia and US to build an honest cost-comparison table against this clinic's own stated pricing (PKR 70/graft per OP-09) - Pakistan comes out roughly 10-40x cheaper per graft even before travel cost, a genuinely strong and truthful hook, no exaggeration needed. Surfaced an operational finding beyond content: the medical visa needs a consent letter from a hospital on Pakistan's Ministry of National Health Services enlisted list - flagged for the clinic to confirm their registration status, since this could be a real patient obstacle, not just missing content. Full draft in docs/seo/content/OP-04-international-patients-page.md, with accommodation and airport-transfer sections left as explicit placeholders rather than invented, since no clinic-specific info on either was available. Not published - needs WordPress access and 3 confirmations from the clinic.</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>docs/seo/content/OP-04-international-patients-page.md; On Page SEO Issue tab row OP-04</t>
+        </is>
+      </c>
+      <c r="G17" s="32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -56702,7 +56743,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J255"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="46" customWidth="1" style="23" min="1" max="1"/>
     <col width="10" customWidth="1" style="23" min="2" max="2"/>

--- a/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
+++ b/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
@@ -855,7 +855,7 @@
       <c r="J6" s="16" t="n"/>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>Drafted ready-to-use byline/medical-reviewer content in docs/seo/content/OP-01-author-bio-boxes.md: a full bio box + short 'Medically reviewed by' line for Dr. Rana Irfan using only confirmed credentials (Immediate Past President ABHRS, FISHRS, 25+ years, real ABHRS/ISHRS/social profile links). Dr. Uzma Irfan's bio is a placeholder only - no confirmed individual credentials for her exist in this engagement, so it's deliberately not filled in. Actual site-wide application needs WordPress/Elementor access this agent doesn't have, and should happen after the OP-02 blog audit (no point bylining a page that's about to be merged/deleted).</t>
+          <t>Drafted ready-to-use byline/medical-reviewer content in docs/seo/content/OP-01-author-bio-boxes.md: a full bio box + short 'Medically reviewed by' line for Dr. Rana Irfan using only confirmed credentials (Immediate Past President ABHRS, FISHRS, 25+ years, real ABHRS/ISHRS/social profile links). Dr. Uzma Irfan's bio is a placeholder only - no confirmed individual credentials for her exist in this engagement, so it's deliberately not filled in. Actual site-wide application needs WordPress/Elementor access this agent doesn't have, and should happen after the OP-02 blog audit (no point bylining a page that's about to be merged/deleted). | UPDATE 2026-10-06: bio upgraded with newly-confirmed facts (HRSP presidency, first non-American ABHRS President, ABHRS Diplomate status) via Dr. Irfan's real IMCAS profile, shared by the user. See updated docs/seo/content/OP-01-author-bio-boxes.md.</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,11 @@
         </is>
       </c>
       <c r="J17" s="16" t="n"/>
-      <c r="K17" s="14" t="n"/>
+      <c r="K17" s="14" t="inlineStr">
+        <is>
+          <t>Candidate sameAs source found 2026-10-06: Dr. Irfan's IMCAS profile (imcas.com/en/profile/dr-rana-irfan-2) - real, well-populated bio confirming ABHRS Diplomate, first non-American ABHRS President, FISHRS, HRSP President (2025). NOT YET confirmed whether the page itself links out to drranairfan.com - checking with the user before adding to the sameAs list. Pending that, combine with the ABHRS/ISHRS profiles already confirmed in OFF-08 for the full Person schema sameAs array.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="45.75" customHeight="1" s="23">
       <c r="A18" s="11" t="inlineStr">
@@ -15018,7 +15022,7 @@
       <c r="J14" s="16" t="n"/>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>Title confirmed by user (2026-09-11): Immediate Past President of ABHRS. Press pitch drafted in docs/seo/outreach/OFF-09-press-pitch.md, targeting Dawn/The News/Express Tribune/Business Recorder/Geo per this row's recommendation. Two claims in the draft (HRSP presidency, procedure count) are flagged as unconfirmed and bracketed for the clinic to verify or remove before sending - not asserted on my own authority. Needs clinic staff to pick a named editor contact per outlet and actually send it.</t>
+          <t>Title confirmed by user (2026-09-11): Immediate Past President of ABHRS. Press pitch drafted in docs/seo/outreach/OFF-09-press-pitch.md, targeting Dawn/The News/Express Tribune/Business Recorder/Geo per this row's recommendation. Two claims in the draft (HRSP presidency, procedure count) are flagged as unconfirmed and bracketed for the clinic to verify or remove before sending - not asserted on my own authority. Needs clinic staff to pick a named editor contact per outlet and actually send it. | UPDATE 2026-10-06: the two previously-unconfirmed facts (HRSP presidency, 'first non-American ABHRS President') are now confirmed via Dr. Irfan's real IMCAS profile (imcas.com/en/profile/dr-rana-irfan-2), shared directly by the user. Pitch rewritten to lead with the stronger 'first non-American' hook. See updated docs/seo/outreach/OFF-09-press-pitch.md.</t>
         </is>
       </c>
     </row>
@@ -56201,7 +56205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="23" min="1" max="1"/>
@@ -56716,6 +56720,43 @@
         </is>
       </c>
       <c r="G17" s="32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="160" customHeight="1" s="23">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>Off Page SEO Issue, On Page SEO Issue</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>OFF-09, OP-01, OP-12</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>Upgraded two credential claims from unconfirmed to confirmed after the user checked a real third-party source (Dr. Irfan's IMCAS profile), and evaluated that profile itself as a potential quality backlink/sameAs source.</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="inlineStr">
+        <is>
+          <t>User shared Dr. Rana Irfan's IMCAS (International Master Course on Aging Science - a real, long-established dermatology/aesthetic medicine conference organization) profile. It independently confirms two facts this agent had previously withheld pending verification: President (2025) of HRSP, and - new information - 'first non-American to serve as President of ABHRS', a stronger press hook than what was drafted. Updated docs/seo/outreach/OFF-09-press-pitch.md (rewritten to lead with the new hook) and docs/seo/content/OP-01-author-bio-boxes.md (bio upgraded) accordingly - both now cite real, confirmed facts rather than carrying CONFIRM placeholders for these two items. Flagged the IMCAS profile itself as a candidate for OP-12's Person schema sameAs list, pending confirmation from the user whether the page actually links back to drranairfan.com (could not verify directly - this environment blocks fetching imcas.com).</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>docs/seo/outreach/OFF-09-press-pitch.md; docs/seo/content/OP-01-author-bio-boxes.md; tracker rows OFF-09, OP-01, OP-12</t>
+        </is>
+      </c>
+      <c r="G18" s="32" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
+++ b/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
@@ -1366,7 +1366,7 @@
       <c r="J17" s="16" t="n"/>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>Candidate sameAs source found 2026-10-06: Dr. Irfan's IMCAS profile (imcas.com/en/profile/dr-rana-irfan-2) - real, well-populated bio confirming ABHRS Diplomate, first non-American ABHRS President, FISHRS, HRSP President (2025). NOT YET confirmed whether the page itself links out to drranairfan.com - checking with the user before adding to the sameAs list. Pending that, combine with the ABHRS/ISHRS profiles already confirmed in OFF-08 for the full Person schema sameAs array.</t>
+          <t>Confirmed by the user (2026-10-06): the IMCAS profile (imcas.com/en/profile/dr-rana-irfan-2) has NO outbound link, but that doesn't block using it as a sameAs source - sameAs is a one-directional assertion from drranairfan.com's own schema pointing at corroborating profiles, it doesn't require the target page to link back. Confirmed candidate for the Person schema sameAs array alongside ABHRS and ISHRS (both from OFF-08). Separately, requesting IMCAS add a link (OFF-08) would make it a real backlink too, but that's a distinct, optional upgrade, not a requirement for using it in schema.</t>
         </is>
       </c>
     </row>
@@ -14973,7 +14973,7 @@
       <c r="J13" s="16" t="n"/>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>Verified via web search (2026-09-11) that both the ABHRS and ISHRS profiles are real and live: abhrs.org/directory/listing/rana-irfan-md and ishrs.org/doctor/594807/. Could not fetch either page directly to check the current outbound link (this environment blocks fetches to arbitrary external domains) so 'does it already link' is still unconfirmed. Drafted ready-to-send outreach emails for both in docs/seo/outreach/OFF-08-society-profile-links.md. HRSP/IBHRS/FACS profile URLs not yet located - same pattern applies once found. Needs clinic staff to actually send + confirm the link was added.</t>
+          <t>Verified via web search (2026-09-11) that both the ABHRS and ISHRS profiles are real and live: abhrs.org/directory/listing/rana-irfan-md and ishrs.org/doctor/594807/. Could not fetch either page directly to check the current outbound link (this environment blocks fetches to arbitrary external domains) so 'does it already link' is still unconfirmed. Drafted ready-to-send outreach emails for both in docs/seo/outreach/OFF-08-society-profile-links.md. HRSP/IBHRS/FACS profile URLs not yet located - same pattern applies once found. Needs clinic staff to actually send + confirm the link was added. | UPDATE 2026-10-06: added IMCAS (imcas.com/en/profile/dr-rana-irfan-2) as a third target - confirmed by the user to be a real, well-populated profile with NO website link currently. Drafted outreach + flagged that the page's 'Sign in' option suggests self-service editing may be possible, worth trying before emailing IMCAS support. See updated docs/seo/outreach/OFF-08-society-profile-links.md.</t>
         </is>
       </c>
     </row>
@@ -56205,7 +56205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="23" min="1" max="1"/>
@@ -56757,6 +56757,43 @@
         </is>
       </c>
       <c r="G18" s="32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="140" customHeight="1" s="23">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>Off Page SEO Issue, On Page SEO Issue</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>OFF-08, OP-12</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>User confirmed the IMCAS profile has no website link. Added it as a third OFF-08 outreach target and clarified it's still valid for OP-12's Person schema regardless.</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>Drafted an outreach request to IMCAS (or self-service edit attempt first, since the page shows a 'Sign in' option) asking them to add the drranairfan.com link - same pattern as the existing ABHRS/ISHRS requests. Separately corrected the framing on OP-12: schema.org sameAs is a one-directional signal from the clinic's own site to corroborating profiles: it does not require the target page to link back, so the IMCAS profile is a confirmed-good sameAs candidate regardless of whether the outreach above succeeds. Updated docs/seo/outreach/OFF-08-society-profile-links.md and tracker rows OFF-08, OP-12.</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>docs/seo/outreach/OFF-08-society-profile-links.md; tracker rows OFF-08, OP-12</t>
+        </is>
+      </c>
+      <c r="G19" s="32" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
+++ b/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
@@ -1366,7 +1366,7 @@
       <c r="J17" s="16" t="n"/>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>Confirmed by the user (2026-10-06): the IMCAS profile (imcas.com/en/profile/dr-rana-irfan-2) has NO outbound link, but that doesn't block using it as a sameAs source - sameAs is a one-directional assertion from drranairfan.com's own schema pointing at corroborating profiles, it doesn't require the target page to link back. Confirmed candidate for the Person schema sameAs array alongside ABHRS and ISHRS (both from OFF-08). Separately, requesting IMCAS add a link (OFF-08) would make it a real backlink too, but that's a distinct, optional upgrade, not a requirement for using it in schema.</t>
+          <t>Confirmed 2026-10-06: the IMCAS profile (imcas.com/en/profile/dr-rana-irfan-2) already links to drranairfan.com (a 'Home' icon) plus Instagram/LinkedIn/Facebook icons to Dr. Irfan's real social profiles - a genuine, already-live backlink from a legitimate international dermatology/aesthetic medicine organization, not just a sameAs candidate. Confirmed for the Person schema sameAs array alongside ABHRS and ISHRS (OFF-08). The page itself isn't indexed by Google yet (no site: search results as of 2026-10-06) - adding a reciprocal link from drranairfan.com (e.g. a Credentials &amp; Affiliations section) would help Google discover/crawl it sooner, as well as being the correct sameAs implementation either way.</t>
         </is>
       </c>
     </row>
@@ -14973,7 +14973,7 @@
       <c r="J13" s="16" t="n"/>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>Verified via web search (2026-09-11) that both the ABHRS and ISHRS profiles are real and live: abhrs.org/directory/listing/rana-irfan-md and ishrs.org/doctor/594807/. Could not fetch either page directly to check the current outbound link (this environment blocks fetches to arbitrary external domains) so 'does it already link' is still unconfirmed. Drafted ready-to-send outreach emails for both in docs/seo/outreach/OFF-08-society-profile-links.md. HRSP/IBHRS/FACS profile URLs not yet located - same pattern applies once found. Needs clinic staff to actually send + confirm the link was added. | UPDATE 2026-10-06: added IMCAS (imcas.com/en/profile/dr-rana-irfan-2) as a third target - confirmed by the user to be a real, well-populated profile with NO website link currently. Drafted outreach + flagged that the page's 'Sign in' option suggests self-service editing may be possible, worth trying before emailing IMCAS support. See updated docs/seo/outreach/OFF-08-society-profile-links.md.</t>
+          <t>Verified via web search (2026-09-11) that both the ABHRS and ISHRS profiles are real and live: abhrs.org/directory/listing/rana-irfan-md and ishrs.org/doctor/594807/. Could not fetch either page directly to check the current outbound link (this environment blocks fetches to arbitrary external domains) so 'does it already link' is still unconfirmed. Drafted ready-to-send outreach emails for both in docs/seo/outreach/OFF-08-society-profile-links.md. HRSP/IBHRS/FACS profile URLs not yet located - same pattern applies once found. Needs clinic staff to actually send + confirm the link was added. | UPDATE 2026-10-06: added IMCAS (imcas.com/en/profile/dr-rana-irfan-2) as a third target - confirmed by the user to be a real, well-populated profile with NO website link currently. Drafted outreach + flagged that the page's 'Sign in' option suggests self-service editing may be possible, worth trying before emailing IMCAS support. See updated docs/seo/outreach/OFF-08-society-profile-links.md. | CORRECTION 2026-10-06: the user confirmed, on closer check, that the IMCAS profile DOES already link to drranairfan.com (via a 'Home' icon), plus Instagram/LinkedIn/Facebook icons to Dr. Irfan's real profiles. The earlier note asking for IMCAS outreach was based on an incomplete first look and is now retracted - no action needed there, it's a confirmed real backlink already. Remaining lever: the page isn't indexed by Google yet (checked via site: search) - linking to it from drranairfan.com would help discovery, see OP-12.</t>
         </is>
       </c>
     </row>
@@ -56205,7 +56205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="23" min="1" max="1"/>
@@ -56794,6 +56794,43 @@
         </is>
       </c>
       <c r="G19" s="32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="160" customHeight="1" s="23">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>Off Page SEO Issue, On Page SEO Issue</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="inlineStr">
+        <is>
+          <t>OFF-08, OP-12</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>Corrected the IMCAS finding after the user checked the page more carefully - it already has a real backlink, contrary to what was logged two entries ago.</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
+        <is>
+          <t>The user initially reported no link visible on the IMCAS profile (based on a partial screenshot); on a closer look, confirmed it actually has a 'Home' icon linking to drranairfan.com plus icons to Dr. Irfan's real Instagram/LinkedIn/Facebook. Retracted the earlier outreach request drafted for IMCAS (not needed - the link already exists) and corrected docs/seo/outreach/OFF-08-society-profile-links.md and tracker rows OFF-08/OP-12 accordingly. This is a genuine, already-live backlink from a legitimate international dermatology/aesthetic medicine organization. Remaining lever: the page itself isn't indexed by Google yet - recommended linking to it from drranairfan.com (Credentials &amp; Affiliations section) to help discovery, which is also the correct sameAs pattern for OP-12 regardless. Exact Instagram/LinkedIn/Facebook URLs from the IMCAS icons not yet obtained - would help resolve OFF-06's wrong-Instagram-handle finding if someone can get them.</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="inlineStr">
+        <is>
+          <t>docs/seo/outreach/OFF-08-society-profile-links.md; tracker rows OFF-08, OP-12</t>
+        </is>
+      </c>
+      <c r="G20" s="32" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
+++ b/docs/seo/DrRanaIrfanSEOIssueTracker.xlsx
@@ -14873,11 +14873,15 @@
       <c r="H11" s="14" t="n"/>
       <c r="I11" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J11" s="16" t="n"/>
-      <c r="K11" s="14" t="n"/>
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>Got exact social URLs from Dr. Irfan's IMCAS profile icons (2026-10-06): LinkedIn linkedin.com/in/dr-rana-irfan-01806427/ (matches an independent source found earlier this session - solid). Facebook facebook.com/ranairfandr/ (new, not seen elsewhere yet - at least confirms a real, specific handle to use instead of the insecure http://fb.com/ link this row originally flagged). CONFLICT found, not resolved: IMCAS's Instagram icon points to 'doctorranairfan' - the SAME handle this row's own evidence calls the WRONG one (vs. the 'official' hairtransplantisb). Either this row's original 'official account' claim needs a second look, or these are genuinely two different real accounts (personal vs. clinic). Needs the clinic to confirm directly which Instagram is actually current before finalizing anywhere (schema, footer links, etc.) - see docs/seo/content/OP-01-author-bio-boxes.md for full detail.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="34.5" customHeight="1" s="23">
       <c r="A12" s="11" t="inlineStr">
@@ -56205,7 +56209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="23" min="1" max="1"/>
@@ -56831,6 +56835,43 @@
         </is>
       </c>
       <c r="G20" s="32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="160" customHeight="1" s="23">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>Off Page SEO Issue, On Page SEO Issue</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>OFF-06, OP-01</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>Got exact social media URLs from the IMCAS profile icons the user checked, and found a real conflict in the process rather than just confirming what was assumed.</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>LinkedIn (linkedin.com/in/dr-rana-irfan-01806427/) and Facebook (facebook.com/ranairfandr/) confirmed via IMCAS's own icons - LinkedIn matches an independent source from earlier in this engagement, Facebook is new and gives OFF-06 a real handle to use instead of the insecure http://fb.com/ link it originally flagged. Added both to the OP-01 bio footer. Instagram is NOT resolved: IMCAS's icon points to 'doctorranairfan', the exact handle OFF-06's own evidence calls the wrong one (vs. 'hairtransplantisb' as official) - flagged as a genuine open conflict in both OFF-06 and OP-01-author-bio-boxes.md rather than silently picking one. Did not guess which is correct - needs the clinic to confirm directly.</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>docs/seo/content/OP-01-author-bio-boxes.md; tracker row OFF-06</t>
+        </is>
+      </c>
+      <c r="G21" s="32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
